--- a/Daily_Report/Top 7 broker List with its Turnover 2024-08-15.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-08-15.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="287">
   <si>
     <t>Date: 2024-08-15</t>
   </si>
@@ -59,109 +59,109 @@
     <t>7</t>
   </si>
   <si>
-    <t>Naasa Securities Co. Ltd.</t>
+    <t>Vision Securities Pvt.Limited</t>
+  </si>
+  <si>
+    <t>Sani Securities Company Limited</t>
   </si>
   <si>
     <t>Imperial Securities Co .Pvt.Limited</t>
   </si>
   <si>
+    <t>Sweta Securities Pvt. Limited</t>
+  </si>
+  <si>
+    <t>Neev Securities Pvt.Ltd</t>
+  </si>
+  <si>
     <t>Online Securities Pvt.Ltd</t>
   </si>
   <si>
-    <t>Vision Securities Pvt.Limited</t>
-  </si>
-  <si>
-    <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
-  </si>
-  <si>
-    <t>Sani Securities Company Limited</t>
-  </si>
-  <si>
-    <t>ABC Securities Pvt. Limited</t>
-  </si>
-  <si>
-    <t>58</t>
+    <t>Dipshika Dhitopatra Karobar Co. Pvt.Limited</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>42</t>
   </si>
   <si>
     <t>45</t>
   </si>
   <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
     <t>49</t>
   </si>
   <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>2,973,784,793.5</t>
-  </si>
-  <si>
-    <t>2,064,713,601.96</t>
-  </si>
-  <si>
-    <t>1,762,455,651.69</t>
-  </si>
-  <si>
-    <t>1,718,993,444.16</t>
-  </si>
-  <si>
-    <t>1,604,537,969.19</t>
-  </si>
-  <si>
-    <t>1,486,958,031.3</t>
-  </si>
-  <si>
-    <t>1,232,997,057.67</t>
-  </si>
-  <si>
-    <t>1,566,702,280.4</t>
-  </si>
-  <si>
-    <t>1,072,018,039.92</t>
-  </si>
-  <si>
-    <t>895,780,883.92</t>
-  </si>
-  <si>
-    <t>794,116,735.86</t>
-  </si>
-  <si>
-    <t>740,692,424.4</t>
-  </si>
-  <si>
-    <t>730,645,242.6</t>
-  </si>
-  <si>
-    <t>722,882,405.3</t>
-  </si>
-  <si>
-    <t>1,407,082,513.1</t>
-  </si>
-  <si>
-    <t>992,695,562.05</t>
-  </si>
-  <si>
-    <t>866,674,767.77</t>
-  </si>
-  <si>
-    <t>924,876,708.3</t>
-  </si>
-  <si>
-    <t>863,845,544.8</t>
-  </si>
-  <si>
-    <t>756,312,788.7</t>
-  </si>
-  <si>
-    <t>510,114,652.37</t>
+    <t>38</t>
+  </si>
+  <si>
+    <t>3,182,864,743.3</t>
+  </si>
+  <si>
+    <t>2,890,919,706.1</t>
+  </si>
+  <si>
+    <t>2,792,021,674.65</t>
+  </si>
+  <si>
+    <t>2,466,952,329.0</t>
+  </si>
+  <si>
+    <t>2,230,422,428.5</t>
+  </si>
+  <si>
+    <t>2,017,438,047.1</t>
+  </si>
+  <si>
+    <t>1,969,795,426.5</t>
+  </si>
+  <si>
+    <t>783,932,266.5</t>
+  </si>
+  <si>
+    <t>1,796,726,978.8</t>
+  </si>
+  <si>
+    <t>2,135,910,178.55</t>
+  </si>
+  <si>
+    <t>243,683,257.8</t>
+  </si>
+  <si>
+    <t>587,031,471.3</t>
+  </si>
+  <si>
+    <t>914,346,427.9</t>
+  </si>
+  <si>
+    <t>548,233,581.2</t>
+  </si>
+  <si>
+    <t>2,398,932,476.8</t>
+  </si>
+  <si>
+    <t>1,094,192,727.3</t>
+  </si>
+  <si>
+    <t>656,111,496.1</t>
+  </si>
+  <si>
+    <t>2,223,269,071.19</t>
+  </si>
+  <si>
+    <t>1,643,390,957.2</t>
+  </si>
+  <si>
+    <t>1,103,091,619.2</t>
+  </si>
+  <si>
+    <t>1,421,561,845.3</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -179,304 +179,367 @@
     <t>% of turnover</t>
   </si>
   <si>
+    <t>CIT</t>
+  </si>
+  <si>
+    <t>213,919,091.8</t>
+  </si>
+  <si>
     <t>SHIVM</t>
   </si>
   <si>
-    <t>109,248,991.4</t>
+    <t>209,519,893.0</t>
+  </si>
+  <si>
+    <t>DORDI</t>
+  </si>
+  <si>
+    <t>56,678,082.0</t>
+  </si>
+  <si>
+    <t>HRL</t>
+  </si>
+  <si>
+    <t>36,927,554.0</t>
+  </si>
+  <si>
+    <t>SGIC</t>
+  </si>
+  <si>
+    <t>33,947,192.2</t>
+  </si>
+  <si>
+    <t>FMDBL</t>
+  </si>
+  <si>
+    <t>792,818,670.0</t>
+  </si>
+  <si>
+    <t>SHEL</t>
+  </si>
+  <si>
+    <t>182,932,310.2</t>
+  </si>
+  <si>
+    <t>MKJC</t>
+  </si>
+  <si>
+    <t>146,628,480.6</t>
+  </si>
+  <si>
+    <t>SMATA</t>
+  </si>
+  <si>
+    <t>112,117,730.0</t>
+  </si>
+  <si>
+    <t>HLI</t>
+  </si>
+  <si>
+    <t>107,204,780.0</t>
   </si>
   <si>
     <t>SHPC</t>
   </si>
   <si>
-    <t>86,739,229.0</t>
+    <t>994,641,153.5</t>
+  </si>
+  <si>
+    <t>RIDI</t>
+  </si>
+  <si>
+    <t>200,544,545.0</t>
+  </si>
+  <si>
+    <t>IHL</t>
+  </si>
+  <si>
+    <t>178,002,377.0</t>
+  </si>
+  <si>
+    <t>MANDU</t>
+  </si>
+  <si>
+    <t>113,795,740.0</t>
+  </si>
+  <si>
+    <t>92,925,813.0</t>
+  </si>
+  <si>
+    <t>LSL</t>
+  </si>
+  <si>
+    <t>116,995,856.2</t>
+  </si>
+  <si>
+    <t>SJCL</t>
+  </si>
+  <si>
+    <t>56,947,960.0</t>
+  </si>
+  <si>
+    <t>15,873,984.0</t>
+  </si>
+  <si>
+    <t>RBCLPO</t>
+  </si>
+  <si>
+    <t>7,232,500.0</t>
+  </si>
+  <si>
+    <t>LICN</t>
+  </si>
+  <si>
+    <t>6,242,754.0</t>
+  </si>
+  <si>
+    <t>CHCL</t>
+  </si>
+  <si>
+    <t>263,571,330.0</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>212,129,127.0</t>
+  </si>
+  <si>
+    <t>MNBBL</t>
+  </si>
+  <si>
+    <t>25,891,200.0</t>
+  </si>
+  <si>
+    <t>SHINE</t>
+  </si>
+  <si>
+    <t>16,228,315.0</t>
+  </si>
+  <si>
+    <t>NIL</t>
+  </si>
+  <si>
+    <t>14,718,805.0</t>
+  </si>
+  <si>
+    <t>GFCL</t>
+  </si>
+  <si>
+    <t>258,962,260.0</t>
+  </si>
+  <si>
+    <t>SPDL</t>
+  </si>
+  <si>
+    <t>225,342,599.7</t>
+  </si>
+  <si>
+    <t>66,960,650.0</t>
+  </si>
+  <si>
+    <t>50,410,798.0</t>
+  </si>
+  <si>
+    <t>HDL</t>
+  </si>
+  <si>
+    <t>41,830,910.0</t>
+  </si>
+  <si>
+    <t>130,766,022.8</t>
+  </si>
+  <si>
+    <t>KSBBL</t>
+  </si>
+  <si>
+    <t>62,800,854.8</t>
+  </si>
+  <si>
+    <t>61,635,705.9</t>
+  </si>
+  <si>
+    <t>GBIME</t>
+  </si>
+  <si>
+    <t>55,703,062.0</t>
+  </si>
+  <si>
+    <t>NMB</t>
+  </si>
+  <si>
+    <t>48,045,252.0</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>1,113,815,579.2</t>
+  </si>
+  <si>
+    <t>JBBL</t>
+  </si>
+  <si>
+    <t>440,471,926.0</t>
+  </si>
+  <si>
+    <t>CHDC</t>
+  </si>
+  <si>
+    <t>308,421,471.0</t>
+  </si>
+  <si>
+    <t>CBBL</t>
+  </si>
+  <si>
+    <t>194,213,422.0</t>
+  </si>
+  <si>
+    <t>64,018,589.6</t>
+  </si>
+  <si>
+    <t>201,547,553.8</t>
+  </si>
+  <si>
+    <t>RADHI</t>
+  </si>
+  <si>
+    <t>142,569,142.79</t>
+  </si>
+  <si>
+    <t>MDB</t>
+  </si>
+  <si>
+    <t>112,367,590.0</t>
+  </si>
+  <si>
+    <t>106,643,273.0</t>
+  </si>
+  <si>
+    <t>PRVU</t>
+  </si>
+  <si>
+    <t>77,354,499.0</t>
+  </si>
+  <si>
+    <t>144,298,420.0</t>
+  </si>
+  <si>
+    <t>NGPL</t>
+  </si>
+  <si>
+    <t>128,490,855.0</t>
+  </si>
+  <si>
+    <t>CLI</t>
+  </si>
+  <si>
+    <t>99,824,932.0</t>
+  </si>
+  <si>
+    <t>87,224,590.0</t>
+  </si>
+  <si>
+    <t>PCBL</t>
+  </si>
+  <si>
+    <t>21,881,722.0</t>
+  </si>
+  <si>
+    <t>1,577,192,415.0</t>
+  </si>
+  <si>
+    <t>SGHC</t>
+  </si>
+  <si>
+    <t>485,557,229.6</t>
+  </si>
+  <si>
+    <t>PPCL</t>
+  </si>
+  <si>
+    <t>78,793,640.0</t>
+  </si>
+  <si>
+    <t>HBL</t>
+  </si>
+  <si>
+    <t>19,372,300.0</t>
+  </si>
+  <si>
+    <t>AHPC</t>
+  </si>
+  <si>
+    <t>5,624,640.0</t>
+  </si>
+  <si>
+    <t>NIMB</t>
+  </si>
+  <si>
+    <t>1,376,484,450.0</t>
+  </si>
+  <si>
+    <t>SANIMA</t>
+  </si>
+  <si>
+    <t>104,405,554.0</t>
+  </si>
+  <si>
+    <t>44,347,287.0</t>
+  </si>
+  <si>
+    <t>39,618,000.0</t>
+  </si>
+  <si>
+    <t>HIDCLP</t>
+  </si>
+  <si>
+    <t>17,801,802.2</t>
+  </si>
+  <si>
+    <t>317,728,341.2</t>
+  </si>
+  <si>
+    <t>229,332,919.5</t>
+  </si>
+  <si>
+    <t>100,736,465.6</t>
+  </si>
+  <si>
+    <t>GCIL</t>
+  </si>
+  <si>
+    <t>74,393,109.0</t>
+  </si>
+  <si>
+    <t>MKHC</t>
+  </si>
+  <si>
+    <t>47,010,191.0</t>
+  </si>
+  <si>
+    <t>352,665,135.6</t>
+  </si>
+  <si>
+    <t>LBBL</t>
+  </si>
+  <si>
+    <t>228,670,928.4</t>
+  </si>
+  <si>
+    <t>163,615,144.0</t>
+  </si>
+  <si>
+    <t>SRLI</t>
+  </si>
+  <si>
+    <t>133,638,934.0</t>
   </si>
   <si>
     <t>KBL</t>
   </si>
   <si>
-    <t>78,759,069.7</t>
-  </si>
-  <si>
-    <t>MEN</t>
-  </si>
-  <si>
-    <t>55,839,676.6</t>
-  </si>
-  <si>
-    <t>UPPER</t>
-  </si>
-  <si>
-    <t>46,115,501.9</t>
-  </si>
-  <si>
-    <t>104,999,151.2</t>
-  </si>
-  <si>
-    <t>HRL</t>
-  </si>
-  <si>
-    <t>77,732,300.59</t>
-  </si>
-  <si>
-    <t>HDL</t>
-  </si>
-  <si>
-    <t>46,913,993.8</t>
-  </si>
-  <si>
-    <t>API</t>
-  </si>
-  <si>
-    <t>32,025,039.8</t>
-  </si>
-  <si>
-    <t>HIDCL</t>
-  </si>
-  <si>
-    <t>30,759,190.9</t>
-  </si>
-  <si>
-    <t>51,566,960.7</t>
-  </si>
-  <si>
-    <t>GBBL</t>
-  </si>
-  <si>
-    <t>39,217,115.0</t>
-  </si>
-  <si>
-    <t>AKPL</t>
-  </si>
-  <si>
-    <t>23,280,555.2</t>
-  </si>
-  <si>
-    <t>AHPC</t>
-  </si>
-  <si>
-    <t>23,009,784.5</t>
-  </si>
-  <si>
-    <t>22,357,431.7</t>
-  </si>
-  <si>
-    <t>33,950,185.7</t>
-  </si>
-  <si>
-    <t>23,088,726.6</t>
-  </si>
-  <si>
-    <t>18,881,220.89</t>
-  </si>
-  <si>
-    <t>SHL</t>
-  </si>
-  <si>
-    <t>18,819,900.5</t>
-  </si>
-  <si>
-    <t>18,476,340.3</t>
-  </si>
-  <si>
-    <t>38,380,709.79</t>
-  </si>
-  <si>
-    <t>35,026,219.1</t>
-  </si>
-  <si>
-    <t>MKJC</t>
-  </si>
-  <si>
-    <t>21,789,014.1</t>
-  </si>
-  <si>
-    <t>21,222,723.89</t>
-  </si>
-  <si>
-    <t>HLI</t>
-  </si>
-  <si>
-    <t>21,130,049.2</t>
-  </si>
-  <si>
-    <t>27,436,358.9</t>
-  </si>
-  <si>
-    <t>24,074,500.2</t>
-  </si>
-  <si>
-    <t>NHPC</t>
-  </si>
-  <si>
-    <t>21,400,697.0</t>
-  </si>
-  <si>
-    <t>21,240,049.2</t>
-  </si>
-  <si>
-    <t>19,749,716.89</t>
-  </si>
-  <si>
-    <t>RADHI</t>
-  </si>
-  <si>
-    <t>37,864,995.1</t>
-  </si>
-  <si>
-    <t>MNBBL</t>
-  </si>
-  <si>
-    <t>35,534,059.5</t>
-  </si>
-  <si>
-    <t>LICN</t>
-  </si>
-  <si>
-    <t>30,618,512.0</t>
-  </si>
-  <si>
-    <t>24,028,357.2</t>
-  </si>
-  <si>
-    <t>KSBBL</t>
-  </si>
-  <si>
-    <t>23,000,072.8</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>135,401,073.9</t>
-  </si>
-  <si>
-    <t>86,074,645.1</t>
-  </si>
-  <si>
-    <t>LBBL</t>
-  </si>
-  <si>
-    <t>60,950,026.7</t>
-  </si>
-  <si>
-    <t>SJLIC</t>
-  </si>
-  <si>
-    <t>37,620,703.9</t>
-  </si>
-  <si>
-    <t>34,606,556.2</t>
-  </si>
-  <si>
-    <t>68,184,412.5</t>
-  </si>
-  <si>
-    <t>63,674,604.3</t>
-  </si>
-  <si>
-    <t>40,472,371.9</t>
-  </si>
-  <si>
-    <t>30,384,322.0</t>
-  </si>
-  <si>
-    <t>JFL</t>
-  </si>
-  <si>
-    <t>29,534,978.2</t>
-  </si>
-  <si>
-    <t>41,463,148.9</t>
-  </si>
-  <si>
-    <t>31,732,838.8</t>
-  </si>
-  <si>
-    <t>30,830,162.8</t>
-  </si>
-  <si>
-    <t>30,258,171.0</t>
-  </si>
-  <si>
-    <t>CHCL</t>
-  </si>
-  <si>
-    <t>26,766,599.5</t>
-  </si>
-  <si>
-    <t>27,025,631.9</t>
-  </si>
-  <si>
-    <t>MFIL</t>
-  </si>
-  <si>
-    <t>24,602,369.7</t>
-  </si>
-  <si>
-    <t>NIFRA</t>
-  </si>
-  <si>
-    <t>23,259,967.8</t>
-  </si>
-  <si>
-    <t>23,035,480.4</t>
-  </si>
-  <si>
-    <t>22,948,765.6</t>
-  </si>
-  <si>
-    <t>54,142,194.1</t>
-  </si>
-  <si>
-    <t>53,917,700.5</t>
-  </si>
-  <si>
-    <t>48,542,669.9</t>
-  </si>
-  <si>
-    <t>35,982,605.7</t>
-  </si>
-  <si>
-    <t>22,230,250.0</t>
-  </si>
-  <si>
-    <t>NLIC</t>
-  </si>
-  <si>
-    <t>30,474,135.4</t>
-  </si>
-  <si>
-    <t>22,930,216.1</t>
-  </si>
-  <si>
-    <t>21,972,640.9</t>
-  </si>
-  <si>
-    <t>20,686,023.6</t>
-  </si>
-  <si>
-    <t>19,779,148.6</t>
-  </si>
-  <si>
-    <t>36,038,940.0</t>
-  </si>
-  <si>
-    <t>26,245,737.1</t>
-  </si>
-  <si>
-    <t>13,541,804.4</t>
-  </si>
-  <si>
-    <t>GCIL</t>
-  </si>
-  <si>
-    <t>13,537,051.0</t>
-  </si>
-  <si>
-    <t>CHDC</t>
-  </si>
-  <si>
-    <t>13,150,452.0</t>
+    <t>116,983,145.2</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -494,331 +557,325 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>865,858,307.7</t>
-  </si>
-  <si>
-    <t>842,972,347.2</t>
-  </si>
-  <si>
-    <t>755,946,669.3</t>
-  </si>
-  <si>
-    <t>NFS</t>
-  </si>
-  <si>
-    <t>616,407,262.79</t>
-  </si>
-  <si>
-    <t>583,292,923.6</t>
+    <t>2,195,306,379.69</t>
+  </si>
+  <si>
+    <t>1,520,032,155.1</t>
+  </si>
+  <si>
+    <t>1,514,027,827.5</t>
+  </si>
+  <si>
+    <t>1,391,864,391.9</t>
+  </si>
+  <si>
+    <t>1,132,705,598.09</t>
+  </si>
+  <si>
+    <t>Promoter Shares/debenture</t>
+  </si>
+  <si>
+    <t>8,318,015,433.65</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>7,033,440,425.6</t>
-  </si>
-  <si>
-    <t>Promoter Shares/debenture</t>
-  </si>
-  <si>
-    <t>5,076,817,521.62</t>
+    <t>8,164,490,177.9</t>
+  </si>
+  <si>
+    <t>Microfinance</t>
+  </si>
+  <si>
+    <t>3,032,329,108.5</t>
+  </si>
+  <si>
+    <t>Development Banks</t>
+  </si>
+  <si>
+    <t>2,163,032,772.19</t>
+  </si>
+  <si>
+    <t>Commercial Banks</t>
+  </si>
+  <si>
+    <t>2,028,915,116.3</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>3,078,632,680.7</t>
-  </si>
-  <si>
-    <t>Development Banks</t>
-  </si>
-  <si>
-    <t>1,385,693,863.3</t>
+    <t>1,266,505,022.9</t>
   </si>
   <si>
     <t>Investment</t>
   </si>
   <si>
-    <t>1,344,468,025.59</t>
+    <t>1,031,826,154.3</t>
   </si>
   <si>
     <t>Manufacturing And Processing</t>
   </si>
   <si>
-    <t>1,253,577,806.4</t>
-  </si>
-  <si>
-    <t>Commercial Banks</t>
-  </si>
-  <si>
-    <t>1,135,986,818.84</t>
-  </si>
-  <si>
-    <t>Microfinance</t>
-  </si>
-  <si>
-    <t>1,068,151,178.6</t>
+    <t>436,877,908.0</t>
   </si>
   <si>
     <t>Non Life Insurance</t>
   </si>
   <si>
-    <t>761,524,328.1</t>
+    <t>184,770,518.5</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>476,020,611.0</t>
+    <t>126,161,561.2</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>79,068,829.09</t>
   </si>
   <si>
     <t>Life Insurance</t>
   </si>
   <si>
-    <t>431,649,869.4</t>
-  </si>
-  <si>
-    <t>Others</t>
-  </si>
-  <si>
-    <t>290,560,602.89</t>
+    <t>70,680,936.8</t>
+  </si>
+  <si>
+    <t>Mutual Fund</t>
+  </si>
+  <si>
+    <t>10,978,424.65</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>60,055,040.1</t>
-  </si>
-  <si>
-    <t>Mutual Fund</t>
-  </si>
-  <si>
-    <t>27,872,037.31</t>
+    <t>10,922,275.0</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>6,130,341.0</t>
+    <t>1,897,325.0</t>
   </si>
   <si>
     <t>Total</t>
   </si>
   <si>
-    <t>23,430,581,150.48</t>
+    <t>29,958,519,216.95</t>
   </si>
   <si>
     <t>100%</t>
   </si>
   <si>
-    <t>541,732,191.7</t>
-  </si>
-  <si>
-    <t>296,998,154.0</t>
-  </si>
-  <si>
-    <t>155,052,473.9</t>
-  </si>
-  <si>
-    <t>145,858,896.8</t>
-  </si>
-  <si>
-    <t>103,702,372.0</t>
-  </si>
-  <si>
-    <t>384,369,476.5</t>
-  </si>
-  <si>
-    <t>234,286,898.0</t>
-  </si>
-  <si>
-    <t>103,119,996.9</t>
-  </si>
-  <si>
-    <t>72,188,049.9</t>
-  </si>
-  <si>
-    <t>58,175,698.9</t>
-  </si>
-  <si>
-    <t>278,402,742.3</t>
-  </si>
-  <si>
-    <t>192,527,989.52</t>
-  </si>
-  <si>
-    <t>106,962,368.3</t>
-  </si>
-  <si>
-    <t>69,612,589.09</t>
-  </si>
-  <si>
-    <t>54,153,460.5</t>
-  </si>
-  <si>
-    <t>236,468,713.6</t>
-  </si>
-  <si>
-    <t>173,162,036.7</t>
-  </si>
-  <si>
-    <t>132,278,548.4</t>
-  </si>
-  <si>
-    <t>37,393,801.5</t>
-  </si>
-  <si>
-    <t>34,712,784.79</t>
-  </si>
-  <si>
-    <t>244,547,131.9</t>
-  </si>
-  <si>
-    <t>169,089,512.6</t>
-  </si>
-  <si>
-    <t>94,749,949.5</t>
-  </si>
-  <si>
-    <t>52,115,993.7</t>
-  </si>
-  <si>
-    <t>36,717,587.9</t>
-  </si>
-  <si>
-    <t>243,095,635.4</t>
-  </si>
-  <si>
-    <t>184,222,100.7</t>
-  </si>
-  <si>
-    <t>74,635,882.2</t>
-  </si>
-  <si>
-    <t>37,759,961.2</t>
-  </si>
-  <si>
-    <t>34,156,398.0</t>
-  </si>
-  <si>
-    <t>185,662,062.7</t>
-  </si>
-  <si>
-    <t>126,250,488.1</t>
-  </si>
-  <si>
-    <t>95,075,230.9</t>
-  </si>
-  <si>
-    <t>76,082,501.4</t>
-  </si>
-  <si>
-    <t>61,624,697.1</t>
-  </si>
-  <si>
-    <t>453,323,112.8</t>
-  </si>
-  <si>
-    <t>305,680,584.7</t>
-  </si>
-  <si>
-    <t>124,943,097.4</t>
-  </si>
-  <si>
-    <t>106,461,279.5</t>
-  </si>
-  <si>
-    <t>97,854,940.5</t>
-  </si>
-  <si>
-    <t>367,957,767.3</t>
-  </si>
-  <si>
-    <t>178,912,465.9</t>
-  </si>
-  <si>
-    <t>131,264,937.3</t>
-  </si>
-  <si>
-    <t>57,051,800.5</t>
-  </si>
-  <si>
-    <t>53,295,368.0</t>
-  </si>
-  <si>
-    <t>334,809,707.0</t>
-  </si>
-  <si>
-    <t>150,037,815.32</t>
-  </si>
-  <si>
-    <t>97,685,573.1</t>
-  </si>
-  <si>
-    <t>56,884,955.8</t>
-  </si>
-  <si>
-    <t>48,568,943.35</t>
-  </si>
-  <si>
-    <t>272,262,980.39</t>
-  </si>
-  <si>
-    <t>216,583,731.4</t>
-  </si>
-  <si>
-    <t>102,958,381.3</t>
-  </si>
-  <si>
-    <t>55,358,238.3</t>
-  </si>
-  <si>
-    <t>46,667,926.1</t>
-  </si>
-  <si>
-    <t>346,910,212.7</t>
-  </si>
-  <si>
-    <t>143,658,362.4</t>
-  </si>
-  <si>
-    <t>103,264,529.1</t>
-  </si>
-  <si>
-    <t>54,731,869.4</t>
-  </si>
-  <si>
-    <t>46,017,691.4</t>
-  </si>
-  <si>
-    <t>221,500,324.9</t>
-  </si>
-  <si>
-    <t>181,089,916.5</t>
-  </si>
-  <si>
-    <t>79,395,659.2</t>
-  </si>
-  <si>
-    <t>55,541,665.0</t>
-  </si>
-  <si>
-    <t>47,654,125.9</t>
-  </si>
-  <si>
-    <t>128,757,420.0</t>
-  </si>
-  <si>
-    <t>123,974,308.2</t>
-  </si>
-  <si>
-    <t>47,272,369.9</t>
-  </si>
-  <si>
-    <t>45,129,719.4</t>
-  </si>
-  <si>
-    <t>37,311,281.4</t>
+    <t>220,445,372.5</t>
+  </si>
+  <si>
+    <t>209,668,730.0</t>
+  </si>
+  <si>
+    <t>154,934,403.0</t>
+  </si>
+  <si>
+    <t>86,258,340.5</t>
+  </si>
+  <si>
+    <t>61,528,331.0</t>
+  </si>
+  <si>
+    <t>994,288,406.0</t>
+  </si>
+  <si>
+    <t>502,346,917.5</t>
+  </si>
+  <si>
+    <t>236,693,721.9</t>
+  </si>
+  <si>
+    <t>17,419,423.5</t>
+  </si>
+  <si>
+    <t>14,500,923.3</t>
+  </si>
+  <si>
+    <t>1,416,414,890.8</t>
+  </si>
+  <si>
+    <t>465,202,863.9</t>
+  </si>
+  <si>
+    <t>132,366,986.3</t>
+  </si>
+  <si>
+    <t>56,342,493.6</t>
+  </si>
+  <si>
+    <t>30,706,888.0</t>
+  </si>
+  <si>
+    <t>130,878,034.7</t>
+  </si>
+  <si>
+    <t>70,703,865.9</t>
+  </si>
+  <si>
+    <t>16,503,192.4</t>
+  </si>
+  <si>
+    <t>7,303,304.0</t>
+  </si>
+  <si>
+    <t>5,371,015.0</t>
+  </si>
+  <si>
+    <t>485,890,175.3</t>
+  </si>
+  <si>
+    <t>43,077,023.0</t>
+  </si>
+  <si>
+    <t>21,272,784.0</t>
+  </si>
+  <si>
+    <t>17,111,386.2</t>
+  </si>
+  <si>
+    <t>6,690,492.7</t>
+  </si>
+  <si>
+    <t>391,586,252.6</t>
+  </si>
+  <si>
+    <t>306,594,996.0</t>
+  </si>
+  <si>
+    <t>66,011,033.2</t>
+  </si>
+  <si>
+    <t>54,762,211.0</t>
+  </si>
+  <si>
+    <t>44,221,725.0</t>
+  </si>
+  <si>
+    <t>172,697,509.3</t>
+  </si>
+  <si>
+    <t>149,752,836.8</t>
+  </si>
+  <si>
+    <t>102,323,224.8</t>
+  </si>
+  <si>
+    <t>57,034,394.2</t>
+  </si>
+  <si>
+    <t>43,947,079.7</t>
+  </si>
+  <si>
+    <t>1,168,721,987.59</t>
+  </si>
+  <si>
+    <t>444,509,319.7</t>
+  </si>
+  <si>
+    <t>316,084,161.39</t>
+  </si>
+  <si>
+    <t>244,507,506.2</t>
+  </si>
+  <si>
+    <t>114,325,248.9</t>
+  </si>
+  <si>
+    <t>338,933,104.0</t>
+  </si>
+  <si>
+    <t>236,813,149.0</t>
+  </si>
+  <si>
+    <t>204,279,507.1</t>
+  </si>
+  <si>
+    <t>179,565,220.9</t>
+  </si>
+  <si>
+    <t>108,533,358.8</t>
+  </si>
+  <si>
+    <t>272,822,516.3</t>
+  </si>
+  <si>
+    <t>167,820,874.1</t>
+  </si>
+  <si>
+    <t>87,475,930.0</t>
+  </si>
+  <si>
+    <t>35,012,469.9</t>
+  </si>
+  <si>
+    <t>27,952,356.0</t>
+  </si>
+  <si>
+    <t>1,593,030,490.7</t>
+  </si>
+  <si>
+    <t>584,914,452.9</t>
+  </si>
+  <si>
+    <t>21,012,896.7</t>
+  </si>
+  <si>
+    <t>10,460,246.0</t>
+  </si>
+  <si>
+    <t>3,457,804.4</t>
+  </si>
+  <si>
+    <t>1,426,329,138.3</t>
+  </si>
+  <si>
+    <t>106,473,143.0</t>
+  </si>
+  <si>
+    <t>57,429,801.2</t>
+  </si>
+  <si>
+    <t>2,987,787.3</t>
+  </si>
+  <si>
+    <t>476,842,308.8</t>
+  </si>
+  <si>
+    <t>384,126,626.8</t>
+  </si>
+  <si>
+    <t>112,849,869.0</t>
+  </si>
+  <si>
+    <t>62,215,278.2</t>
+  </si>
+  <si>
+    <t>45,191,860.7</t>
+  </si>
+  <si>
+    <t>598,304,481.9</t>
+  </si>
+  <si>
+    <t>299,628,610.39</t>
+  </si>
+  <si>
+    <t>232,901,174.7</t>
+  </si>
+  <si>
+    <t>170,930,359.6</t>
+  </si>
+  <si>
+    <t>91,256,539.0</t>
   </si>
 </sst>
 </file>
@@ -1627,61 +1684,61 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.03673735626020848</v>
+        <v>0.06720960802695257</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G9" s="12">
-        <v>0.05085409961934548</v>
+        <v>0.274244444882751</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J9" s="14">
-        <v>0.02925858625183164</v>
+        <v>0.3562440659149559</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="M9" s="16">
-        <v>0.0197500379162819</v>
+        <v>0.04742526023898697</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="P9" s="18">
-        <v>0.02392010069985199</v>
+        <v>0.1181710364064338</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="S9" s="16">
-        <v>0.0184513337447818</v>
+        <v>0.1283619392289392</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="V9" s="18">
-        <v>0.03070972056620609</v>
+        <v>0.06638558554902807</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1693,61 +1750,61 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.02916795767790317</v>
+        <v>0.06582745730588896</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G10" s="12">
-        <v>0.03764798203771869</v>
+        <v>0.06327823972903943</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J10" s="14">
-        <v>0.02225140528352876</v>
+        <v>0.07182771782211887</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="M10" s="16">
-        <v>0.0134315384845941</v>
+        <v>0.02308433743552894</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="P10" s="18">
-        <v>0.0218294735134648</v>
+        <v>0.09510715292737651</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="S10" s="16">
-        <v>0.01619043691431723</v>
+        <v>0.1116974075233301</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="V10" s="18">
-        <v>0.02881925733638721</v>
+        <v>0.03188191725654817</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1759,61 +1816,61 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.02648445505274926</v>
+        <v>0.01780725433567625</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G11" s="12">
-        <v>0.02272179238575174</v>
+        <v>0.0507203573626088</v>
       </c>
       <c r="H11" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="J11" s="14">
+        <v>0.0637539380930178</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="M11" s="16">
+        <v>0.006434653727757542</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="O11" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="P11" s="18">
+        <v>0.01160820464731979</v>
+      </c>
+      <c r="Q11" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="I11" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="J11" s="14">
-        <v>0.01320915801636003</v>
-      </c>
-      <c r="K11" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="L11" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="M11" s="16">
-        <v>0.01098388185489937</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="O11" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="P11" s="18">
-        <v>0.01357961887985966</v>
-      </c>
-      <c r="Q11" s="15" t="s">
-        <v>96</v>
-      </c>
       <c r="R11" s="15" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="S11" s="16">
-        <v>0.01439226699713243</v>
+        <v>0.03319093247807719</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="V11" s="18">
-        <v>0.02483259129414302</v>
+        <v>0.0312904096896582</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1825,61 +1882,61 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.01877730921284301</v>
+        <v>0.01160198656814849</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G12" s="12">
-        <v>0.01551064504512589</v>
+        <v>0.03878272017151684</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J12" s="14">
-        <v>0.01305552538467346</v>
+        <v>0.04075747012754301</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="M12" s="16">
-        <v>0.01094820958389198</v>
+        <v>0.002931755070813126</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="P12" s="18">
-        <v>0.01322668849686452</v>
+        <v>0.007275893029336976</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="S12" s="16">
-        <v>0.01428422911266063</v>
+        <v>0.02498753211899808</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="V12" s="18">
-        <v>0.01948776523879667</v>
+        <v>0.02827860256482325</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1891,61 +1948,61 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.01550734336956653</v>
+        <v>0.01066560942354198</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G13" s="12">
-        <v>0.01489755812653717</v>
+        <v>0.03708327829852624</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J13" s="14">
-        <v>0.01268538682296017</v>
+        <v>0.03328262593507585</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="M13" s="16">
-        <v>0.01074834832137979</v>
+        <v>0.002530553155249073</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="P13" s="18">
-        <v>0.01316893062401954</v>
+        <v>0.006599110918149557</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01328195986993221</v>
+        <v>0.02073466893326937</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="V13" s="18">
-        <v>0.01865379374340385</v>
+        <v>0.0243909856595456</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1956,7 +2013,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -1965,7 +2022,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -1974,7 +2031,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -1983,7 +2040,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -1992,7 +2049,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2001,7 +2058,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2010,7 +2067,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2019,566 +2076,566 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D16" s="10">
-        <v>0.04553156442118985</v>
+        <v>0.3499412224614967</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="G16" s="12">
-        <v>0.03302366605951711</v>
+        <v>0.06971745129230797</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="J16" s="14">
-        <v>0.02352578282479983</v>
+        <v>0.05168241396911392</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="M16" s="16">
-        <v>0.01572177717827557</v>
+        <v>0.6393282904008641</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>56</v>
+        <v>152</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="P16" s="18">
-        <v>0.03374316790209368</v>
+        <v>0.6171406960455069</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="S16" s="16">
-        <v>0.02049428077896552</v>
+        <v>0.157491002837348</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="V16" s="18">
-        <v>0.0292287315495326</v>
+        <v>0.1790364272632247</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="D17" s="10">
-        <v>0.02894447684584947</v>
+        <v>0.138388515228994</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="G17" s="12">
-        <v>0.03083943663627067</v>
+        <v>0.0493161890657742</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>69</v>
+        <v>136</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="J17" s="14">
-        <v>0.01800490058831932</v>
+        <v>0.04602072260635557</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="M17" s="16">
-        <v>0.01431207884101161</v>
+        <v>0.1968247314275525</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>89</v>
+        <v>154</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="P17" s="18">
-        <v>0.03360325622389766</v>
+        <v>0.04680976691496716</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="S17" s="16">
-        <v>0.015420889909013</v>
+        <v>0.1136753219409431</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>65</v>
+        <v>168</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="V17" s="18">
-        <v>0.02128613116855014</v>
+        <v>0.1160886685610345</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="D18" s="10">
-        <v>0.02049577589919168</v>
+        <v>0.09690058983789177</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>54</v>
+        <v>130</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="G18" s="12">
-        <v>0.01960193019573475</v>
+        <v>0.03886914941390388</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="J18" s="14">
-        <v>0.01749273110528329</v>
+        <v>0.03575363791275502</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="M18" s="16">
-        <v>0.01353115561843586</v>
+        <v>0.0319396686647527</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="P18" s="18">
-        <v>0.03025336316859033</v>
+        <v>0.01988290936879807</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="S18" s="16">
-        <v>0.0147769072411479</v>
+        <v>0.04993286695708219</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="V18" s="18">
-        <v>0.01098283594089836</v>
+        <v>0.08306199811353862</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="D19" s="10">
-        <v>0.0126507822564128</v>
+        <v>0.06101843391517767</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="G19" s="12">
-        <v>0.01471599836946368</v>
+        <v>0.03688904703059612</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="J19" s="14">
-        <v>0.01716818858448197</v>
+        <v>0.03124065647195745</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="M19" s="16">
-        <v>0.01340056326465891</v>
+        <v>0.007852725718397941</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>54</v>
+        <v>146</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="P19" s="18">
-        <v>0.02242552460004448</v>
+        <v>0.01776255452499365</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>54</v>
+        <v>163</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="S19" s="16">
-        <v>0.01391163917512512</v>
+        <v>0.03687504015646856</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="V19" s="18">
-        <v>0.01097898078165817</v>
+        <v>0.06784406756261702</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D20" s="10">
-        <v>0.01163720934872014</v>
+        <v>0.02011351243710891</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="G20" s="12">
-        <v>0.01430463681346404</v>
+        <v>0.0267577473136932</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="J20" s="14">
-        <v>0.01518710526096574</v>
+        <v>0.007837232138515912</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>62</v>
+        <v>150</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="M20" s="16">
-        <v>0.0133501181624425</v>
+        <v>0.002279995415347161</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>71</v>
+        <v>158</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="P20" s="18">
-        <v>0.01385461137518839</v>
+        <v>0.007981359034293803</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="S20" s="16">
-        <v>0.0133017530983761</v>
+        <v>0.02330192546312666</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="V20" s="18">
-        <v>0.01066543664333674</v>
+        <v>0.05938847436957434</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="D31" s="22">
-        <v>0.3001820731815656</v>
+        <v>0.2776510872721578</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="D32" s="22">
-        <v>0.2166748442565197</v>
+        <v>0.2725264930077277</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="D33" s="22">
-        <v>0.1313937823790141</v>
+        <v>0.1012175897794161</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="D34" s="22">
-        <v>0.05914039666368295</v>
+        <v>0.07220092410228988</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="D35" s="22">
-        <v>0.05738090818001145</v>
+        <v>0.06772414556297815</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="D36" s="22">
-        <v>0.05350178035914057</v>
+        <v>0.0422752878314304</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="D37" s="22">
-        <v>0.04848308334967304</v>
+        <v>0.03444182760929689</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="D38" s="22">
-        <v>0.04558790803095884</v>
+        <v>0.01458276041069554</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="D39" s="22">
-        <v>0.03250129918712662</v>
+        <v>0.0061675451033461</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="D40" s="22">
-        <v>0.02031621016750787</v>
+        <v>0.004211208180430361</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="D41" s="22">
-        <v>0.01842249949447614</v>
+        <v>0.002639276945813271</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="D42" s="22">
-        <v>0.01240091319263106</v>
+        <v>0.002359293404595577</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="D43" s="22">
-        <v>0.002563105017084466</v>
+        <v>0.0003664541818805451</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="D44" s="22">
-        <v>0.001189558087825278</v>
+        <v>0.0003645799353734536</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="D45" s="22">
-        <v>0.000261638452782227</v>
+        <v>6.33317349986553E-05</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -2957,331 +3014,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>165</v>
+        <v>197</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1821692655380108</v>
+        <v>0.06926005038826809</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="G9" s="12">
-        <v>0.1861611586872206</v>
+        <v>0.3439349781669815</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1579629774133849</v>
+        <v>0.5073079853427562</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1375623126448585</v>
+        <v>0.05305251875420411</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1524096883926828</v>
+        <v>0.2178467043244225</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1634852028657925</v>
+        <v>0.1941007572266679</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1505778635440107</v>
+        <v>0.08767281463682493</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="D10" s="10">
-        <v>0.09987210730553492</v>
+        <v>0.06587421926783325</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="G10" s="12">
-        <v>0.1134718625268223</v>
+        <v>0.1737671635915796</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="J10" s="14">
-        <v>0.1092384874112361</v>
+        <v>0.1666186434452793</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="M10" s="16">
-        <v>0.10073455328657</v>
+        <v>0.02866041028391514</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="P10" s="18">
-        <v>0.1053820575428986</v>
+        <v>0.0193133921402369</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>167</v>
+        <v>195</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="S10" s="16">
-        <v>0.1238919302510108</v>
+        <v>0.1519724466586323</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="V10" s="18">
-        <v>0.10239317873035</v>
+        <v>0.07602456315277673</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="D11" s="10">
-        <v>0.05213977630086365</v>
+        <v>0.04867765849181631</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="G11" s="12">
-        <v>0.04994397130992424</v>
+        <v>0.08187488618260937</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="J11" s="14">
-        <v>0.06068939561539317</v>
+        <v>0.04740901100511447</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="M11" s="16">
-        <v>0.07695116514224927</v>
+        <v>0.006689708676571674</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="P11" s="18">
-        <v>0.05905123550752806</v>
+        <v>0.009537558324458895</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="S11" s="16">
-        <v>0.05019367099066557</v>
+        <v>0.03272022816011062</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="V11" s="18">
-        <v>0.07710904929462208</v>
+        <v>0.05194611756298542</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="D12" s="10">
-        <v>0.04904823547380212</v>
+        <v>0.02710085016385811</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="G12" s="12">
-        <v>0.034962742450635</v>
+        <v>0.006025564619883443</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="J12" s="14">
-        <v>0.03949749829633967</v>
+        <v>0.02017981955926719</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>177</v>
+        <v>207</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="M12" s="16">
-        <v>0.02175331245563463</v>
+        <v>0.002960456071301733</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="P12" s="18">
-        <v>0.03248037422634773</v>
+        <v>0.007671814083894287</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="S12" s="16">
-        <v>0.02539410017308133</v>
+        <v>0.02714443255331625</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="V12" s="18">
-        <v>0.06170533897605031</v>
+        <v>0.02895447589770308</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="D13" s="10">
-        <v>0.03487218450597676</v>
+        <v>0.01933111707920309</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="G13" s="12">
-        <v>0.02817615907818545</v>
+        <v>0.005016024232496756</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="J13" s="14">
-        <v>0.03072614079569765</v>
+        <v>0.01099808367492324</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="M13" s="16">
-        <v>0.02019366910207309</v>
+        <v>0.002177186375618854</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="P13" s="18">
-        <v>0.02288358929786303</v>
+        <v>0.002999652718027714</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="S13" s="16">
-        <v>0.02297065369769592</v>
+        <v>0.02191974373813722</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="V13" s="18">
-        <v>0.04997959785601797</v>
+        <v>0.02231047910294252</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3292,7 +3349,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3301,7 +3358,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3310,7 +3367,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3319,7 +3376,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3328,7 +3385,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3337,7 +3394,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3346,7 +3403,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3355,331 +3412,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="D16" s="10">
-        <v>0.1524397844090328</v>
+        <v>0.3671918481802235</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="G16" s="12">
-        <v>0.1782124973405132</v>
+        <v>0.1172405803194162</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="J16" s="14">
-        <v>0.1899677343250904</v>
+        <v>0.09771504239278525</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="M16" s="16">
-        <v>0.1583851185267571</v>
+        <v>0.6457483883953884</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="P16" s="18">
-        <v>0.2162056737572652</v>
+        <v>0.6394883408965863</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="S16" s="16">
-        <v>0.1489620555775534</v>
+        <v>0.2363603231759434</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="V16" s="18">
-        <v>0.104426380581405</v>
+        <v>0.3037394004732196</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="D17" s="10">
-        <v>0.1027917640066445</v>
+        <v>0.1396569931649473</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>167</v>
+        <v>193</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="G17" s="12">
-        <v>0.0866524372820011</v>
+        <v>0.08191619729192451</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="J17" s="14">
-        <v>0.08512998053376851</v>
+        <v>0.06010729630923712</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="M17" s="16">
-        <v>0.1259945069225296</v>
+        <v>0.2371000225760747</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>167</v>
+        <v>193</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="P17" s="18">
-        <v>0.08953254155252309</v>
+        <v>0.04773676126974976</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="S17" s="16">
-        <v>0.1217854927228032</v>
+        <v>0.190403183558558</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="V17" s="18">
-        <v>0.1005471241223193</v>
+        <v>0.152111537253587</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="D18" s="10">
-        <v>0.04201484171722731</v>
+        <v>0.09930807209617186</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="G18" s="12">
-        <v>0.0635753729595991</v>
+        <v>0.07066246311475168</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="J18" s="14">
-        <v>0.05542583327207713</v>
+        <v>0.03133067726308598</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="M18" s="16">
-        <v>0.05989457472905689</v>
+        <v>0.008517755472201505</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="P18" s="18">
-        <v>0.06435779712429382</v>
+        <v>0.02574839656657443</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="S18" s="16">
-        <v>0.05339468736087118</v>
+        <v>0.05593721659121971</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>265</v>
+        <v>284</v>
       </c>
       <c r="V18" s="18">
-        <v>0.03833940203339236</v>
+        <v>0.1182362247199582</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="D19" s="10">
-        <v>0.03579992732920671</v>
+        <v>0.07681994866878765</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="G19" s="12">
-        <v>0.02763182285696443</v>
+        <v>0.06211352758124257</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="J19" s="14">
-        <v>0.03227596435998467</v>
+        <v>0.01254018556442226</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="M19" s="16">
-        <v>0.03220386819279072</v>
+        <v>0.004240149222599753</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>256</v>
+        <v>156</v>
       </c>
       <c r="P19" s="18">
-        <v>0.03411067263636556</v>
+        <v>0.01988290936879807</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="S19" s="16">
-        <v>0.03735254380477819</v>
+        <v>0.03083875526657802</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>266</v>
+        <v>285</v>
       </c>
       <c r="V19" s="18">
-        <v>0.03660164403415676</v>
+        <v>0.08677569117099379</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="D20" s="10">
-        <v>0.03290585812190851</v>
+        <v>0.03591897806548555</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="G20" s="12">
-        <v>0.0258124748871463</v>
+        <v>0.03754284789404169</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="J20" s="14">
-        <v>0.0275575406980753</v>
+        <v>0.01001151110458483</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="M20" s="16">
-        <v>0.02714840260650596</v>
+        <v>0.001401650270802618</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="P20" s="18">
-        <v>0.02867971483588124</v>
+        <v>0.001339561179901397</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="S20" s="16">
-        <v>0.03204806383024644</v>
+        <v>0.02240061882691357</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>267</v>
+        <v>286</v>
       </c>
       <c r="V20" s="18">
-        <v>0.03026064106795785</v>
+        <v>0.04632792714020448</v>
       </c>
     </row>
   </sheetData>

--- a/Daily_Report/Top 7 broker List with its Turnover 2024-08-15.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-08-15.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="282">
   <si>
     <t>Date: 2024-08-15</t>
   </si>
@@ -59,109 +59,109 @@
     <t>7</t>
   </si>
   <si>
+    <t>Kohinoor Investment and Securities Pvt.Ltd</t>
+  </si>
+  <si>
+    <t>Naasa Securities Co. Ltd.</t>
+  </si>
+  <si>
+    <t>Imperial Securities Co .Pvt.Limited</t>
+  </si>
+  <si>
+    <t>Primo Securities Pvt. Limited</t>
+  </si>
+  <si>
     <t>Vision Securities Pvt.Limited</t>
   </si>
   <si>
+    <t>Sumeru Securities Pvt.Limited</t>
+  </si>
+  <si>
     <t>Sani Securities Company Limited</t>
   </si>
   <si>
-    <t>Imperial Securities Co .Pvt.Limited</t>
-  </si>
-  <si>
-    <t>Sweta Securities Pvt. Limited</t>
-  </si>
-  <si>
-    <t>Neev Securities Pvt.Ltd</t>
-  </si>
-  <si>
-    <t>Online Securities Pvt.Ltd</t>
-  </si>
-  <si>
-    <t>Dipshika Dhitopatra Karobar Co. Pvt.Limited</t>
+    <t>35</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>16</t>
   </si>
   <si>
     <t>34</t>
   </si>
   <si>
+    <t>39</t>
+  </si>
+  <si>
     <t>42</t>
   </si>
   <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>3,182,864,743.3</t>
-  </si>
-  <si>
-    <t>2,890,919,706.1</t>
-  </si>
-  <si>
-    <t>2,792,021,674.65</t>
-  </si>
-  <si>
-    <t>2,466,952,329.0</t>
-  </si>
-  <si>
-    <t>2,230,422,428.5</t>
-  </si>
-  <si>
-    <t>2,017,438,047.1</t>
-  </si>
-  <si>
-    <t>1,969,795,426.5</t>
-  </si>
-  <si>
-    <t>783,932,266.5</t>
-  </si>
-  <si>
-    <t>1,796,726,978.8</t>
-  </si>
-  <si>
-    <t>2,135,910,178.55</t>
-  </si>
-  <si>
-    <t>243,683,257.8</t>
-  </si>
-  <si>
-    <t>587,031,471.3</t>
-  </si>
-  <si>
-    <t>914,346,427.9</t>
-  </si>
-  <si>
-    <t>548,233,581.2</t>
-  </si>
-  <si>
-    <t>2,398,932,476.8</t>
-  </si>
-  <si>
-    <t>1,094,192,727.3</t>
-  </si>
-  <si>
-    <t>656,111,496.1</t>
-  </si>
-  <si>
-    <t>2,223,269,071.19</t>
-  </si>
-  <si>
-    <t>1,643,390,957.2</t>
-  </si>
-  <si>
-    <t>1,103,091,619.2</t>
-  </si>
-  <si>
-    <t>1,421,561,845.3</t>
+    <t>4,404,716,765.0</t>
+  </si>
+  <si>
+    <t>3,867,295,958.8</t>
+  </si>
+  <si>
+    <t>3,165,137,789.25</t>
+  </si>
+  <si>
+    <t>3,028,826,230.2</t>
+  </si>
+  <si>
+    <t>2,853,388,226.2</t>
+  </si>
+  <si>
+    <t>2,217,046,780.19</t>
+  </si>
+  <si>
+    <t>1,923,238,230.3</t>
+  </si>
+  <si>
+    <t>465,655,045.0</t>
+  </si>
+  <si>
+    <t>1,818,884,980.8</t>
+  </si>
+  <si>
+    <t>1,770,672,467.35</t>
+  </si>
+  <si>
+    <t>2,278,706,766.4</t>
+  </si>
+  <si>
+    <t>1,667,441,090.6</t>
+  </si>
+  <si>
+    <t>756,052,820.8</t>
+  </si>
+  <si>
+    <t>1,552,730,318.4</t>
+  </si>
+  <si>
+    <t>3,939,061,720.0</t>
+  </si>
+  <si>
+    <t>2,048,410,978.0</t>
+  </si>
+  <si>
+    <t>1,394,465,321.9</t>
+  </si>
+  <si>
+    <t>750,119,463.8</t>
+  </si>
+  <si>
+    <t>1,185,947,135.59</t>
+  </si>
+  <si>
+    <t>1,460,993,959.4</t>
+  </si>
+  <si>
+    <t>370,507,911.9</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -179,367 +179,352 @@
     <t>% of turnover</t>
   </si>
   <si>
-    <t>CIT</t>
-  </si>
-  <si>
-    <t>213,919,091.8</t>
-  </si>
-  <si>
-    <t>SHIVM</t>
-  </si>
-  <si>
-    <t>209,519,893.0</t>
-  </si>
-  <si>
-    <t>DORDI</t>
-  </si>
-  <si>
-    <t>56,678,082.0</t>
+    <t>HLI</t>
+  </si>
+  <si>
+    <t>171,344,790.6</t>
+  </si>
+  <si>
+    <t>HDHPC</t>
+  </si>
+  <si>
+    <t>77,141,032.5</t>
+  </si>
+  <si>
+    <t>MEN</t>
+  </si>
+  <si>
+    <t>46,613,807.0</t>
+  </si>
+  <si>
+    <t>NRM</t>
+  </si>
+  <si>
+    <t>19,618,915.0</t>
+  </si>
+  <si>
+    <t>SPIL</t>
+  </si>
+  <si>
+    <t>14,766,656.5</t>
+  </si>
+  <si>
+    <t>NRIC</t>
+  </si>
+  <si>
+    <t>428,407,353.4</t>
+  </si>
+  <si>
+    <t>JBLB</t>
+  </si>
+  <si>
+    <t>231,099,825.8</t>
+  </si>
+  <si>
+    <t>143,427,568.4</t>
+  </si>
+  <si>
+    <t>HIDCL</t>
+  </si>
+  <si>
+    <t>134,855,499.3</t>
+  </si>
+  <si>
+    <t>SHINE</t>
+  </si>
+  <si>
+    <t>112,069,508.5</t>
+  </si>
+  <si>
+    <t>511,401,939.7</t>
+  </si>
+  <si>
+    <t>359,565,809.6</t>
+  </si>
+  <si>
+    <t>SHPC</t>
+  </si>
+  <si>
+    <t>188,990,608.5</t>
+  </si>
+  <si>
+    <t>NABIL</t>
+  </si>
+  <si>
+    <t>150,675,229.19</t>
+  </si>
+  <si>
+    <t>PRIN</t>
+  </si>
+  <si>
+    <t>69,226,046.0</t>
+  </si>
+  <si>
+    <t>NFS</t>
+  </si>
+  <si>
+    <t>926,822,250.0</t>
+  </si>
+  <si>
+    <t>NMB</t>
+  </si>
+  <si>
+    <t>630,026,634.0</t>
+  </si>
+  <si>
+    <t>MFIL</t>
+  </si>
+  <si>
+    <t>392,651,245.0</t>
+  </si>
+  <si>
+    <t>SPHL</t>
+  </si>
+  <si>
+    <t>68,423,940.0</t>
+  </si>
+  <si>
+    <t>KBL</t>
+  </si>
+  <si>
+    <t>45,792,940.0</t>
+  </si>
+  <si>
+    <t>RHPL</t>
+  </si>
+  <si>
+    <t>623,728,130.0</t>
+  </si>
+  <si>
+    <t>NBL</t>
+  </si>
+  <si>
+    <t>185,560,471.6</t>
+  </si>
+  <si>
+    <t>142,890,412.69</t>
+  </si>
+  <si>
+    <t>SONA</t>
+  </si>
+  <si>
+    <t>129,323,791.8</t>
+  </si>
+  <si>
+    <t>111,610,720.0</t>
+  </si>
+  <si>
+    <t>230,469,742.0</t>
+  </si>
+  <si>
+    <t>GUFL</t>
+  </si>
+  <si>
+    <t>196,429,235.0</t>
+  </si>
+  <si>
+    <t>STC</t>
+  </si>
+  <si>
+    <t>75,536,585.0</t>
+  </si>
+  <si>
+    <t>AHPC</t>
+  </si>
+  <si>
+    <t>51,709,632.0</t>
+  </si>
+  <si>
+    <t>AKJCL</t>
+  </si>
+  <si>
+    <t>24,637,218.0</t>
+  </si>
+  <si>
+    <t>647,465,262.1</t>
+  </si>
+  <si>
+    <t>SGHC</t>
+  </si>
+  <si>
+    <t>147,338,724.6</t>
+  </si>
+  <si>
+    <t>PRVU</t>
+  </si>
+  <si>
+    <t>124,958,226.3</t>
+  </si>
+  <si>
+    <t>CHDC</t>
+  </si>
+  <si>
+    <t>87,326,800.0</t>
+  </si>
+  <si>
+    <t>78,009,317.0</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>2,559,822,904.4</t>
+  </si>
+  <si>
+    <t>928,230,650.0</t>
+  </si>
+  <si>
+    <t>NIFRA</t>
+  </si>
+  <si>
+    <t>155,633,041.19</t>
+  </si>
+  <si>
+    <t>GBLBS</t>
+  </si>
+  <si>
+    <t>31,576,800.0</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>23,153,395.3</t>
+  </si>
+  <si>
+    <t>645,023,489.79</t>
+  </si>
+  <si>
+    <t>487,466,815.4</t>
+  </si>
+  <si>
+    <t>ADBL</t>
+  </si>
+  <si>
+    <t>129,841,944.8</t>
+  </si>
+  <si>
+    <t>116,442,915.2</t>
+  </si>
+  <si>
+    <t>80,605,665.0</t>
+  </si>
+  <si>
+    <t>604,706,088.29</t>
+  </si>
+  <si>
+    <t>195,612,824.0</t>
+  </si>
+  <si>
+    <t>UPPER</t>
+  </si>
+  <si>
+    <t>76,598,601.5</t>
+  </si>
+  <si>
+    <t>MHCL</t>
+  </si>
+  <si>
+    <t>45,617,806.0</t>
+  </si>
+  <si>
+    <t>GHL</t>
+  </si>
+  <si>
+    <t>39,221,033.29</t>
+  </si>
+  <si>
+    <t>456,936,405.0</t>
+  </si>
+  <si>
+    <t>57,506,828.0</t>
+  </si>
+  <si>
+    <t>NGPL</t>
+  </si>
+  <si>
+    <t>49,627,753.0</t>
+  </si>
+  <si>
+    <t>32,695,849.0</t>
   </si>
   <si>
     <t>HRL</t>
   </si>
   <si>
-    <t>36,927,554.0</t>
-  </si>
-  <si>
-    <t>SGIC</t>
-  </si>
-  <si>
-    <t>33,947,192.2</t>
-  </si>
-  <si>
-    <t>FMDBL</t>
-  </si>
-  <si>
-    <t>792,818,670.0</t>
-  </si>
-  <si>
-    <t>SHEL</t>
-  </si>
-  <si>
-    <t>182,932,310.2</t>
-  </si>
-  <si>
-    <t>MKJC</t>
-  </si>
-  <si>
-    <t>146,628,480.6</t>
-  </si>
-  <si>
-    <t>SMATA</t>
-  </si>
-  <si>
-    <t>112,117,730.0</t>
-  </si>
-  <si>
-    <t>HLI</t>
-  </si>
-  <si>
-    <t>107,204,780.0</t>
-  </si>
-  <si>
-    <t>SHPC</t>
-  </si>
-  <si>
-    <t>994,641,153.5</t>
-  </si>
-  <si>
-    <t>RIDI</t>
-  </si>
-  <si>
-    <t>200,544,545.0</t>
-  </si>
-  <si>
-    <t>IHL</t>
-  </si>
-  <si>
-    <t>178,002,377.0</t>
-  </si>
-  <si>
-    <t>MANDU</t>
-  </si>
-  <si>
-    <t>113,795,740.0</t>
-  </si>
-  <si>
-    <t>92,925,813.0</t>
-  </si>
-  <si>
-    <t>LSL</t>
-  </si>
-  <si>
-    <t>116,995,856.2</t>
-  </si>
-  <si>
-    <t>SJCL</t>
-  </si>
-  <si>
-    <t>56,947,960.0</t>
-  </si>
-  <si>
-    <t>15,873,984.0</t>
-  </si>
-  <si>
-    <t>RBCLPO</t>
-  </si>
-  <si>
-    <t>7,232,500.0</t>
-  </si>
-  <si>
-    <t>LICN</t>
-  </si>
-  <si>
-    <t>6,242,754.0</t>
-  </si>
-  <si>
-    <t>CHCL</t>
-  </si>
-  <si>
-    <t>263,571,330.0</t>
-  </si>
-  <si>
-    <t>API</t>
-  </si>
-  <si>
-    <t>212,129,127.0</t>
-  </si>
-  <si>
-    <t>MNBBL</t>
-  </si>
-  <si>
-    <t>25,891,200.0</t>
-  </si>
-  <si>
-    <t>SHINE</t>
-  </si>
-  <si>
-    <t>16,228,315.0</t>
-  </si>
-  <si>
-    <t>NIL</t>
-  </si>
-  <si>
-    <t>14,718,805.0</t>
+    <t>11,058,681.0</t>
+  </si>
+  <si>
+    <t>PCBL</t>
+  </si>
+  <si>
+    <t>187,462,710.2</t>
+  </si>
+  <si>
+    <t>BGWT</t>
+  </si>
+  <si>
+    <t>184,327,910.0</t>
+  </si>
+  <si>
+    <t>123,407,558.8</t>
+  </si>
+  <si>
+    <t>RADHI</t>
+  </si>
+  <si>
+    <t>102,896,393.6</t>
+  </si>
+  <si>
+    <t>SCB</t>
+  </si>
+  <si>
+    <t>47,550,724.0</t>
+  </si>
+  <si>
+    <t>505,323,804.0</t>
+  </si>
+  <si>
+    <t>369,488,190.2</t>
   </si>
   <si>
     <t>GFCL</t>
   </si>
   <si>
-    <t>258,962,260.0</t>
-  </si>
-  <si>
-    <t>SPDL</t>
-  </si>
-  <si>
-    <t>225,342,599.7</t>
-  </si>
-  <si>
-    <t>66,960,650.0</t>
-  </si>
-  <si>
-    <t>50,410,798.0</t>
-  </si>
-  <si>
-    <t>HDL</t>
-  </si>
-  <si>
-    <t>41,830,910.0</t>
-  </si>
-  <si>
-    <t>130,766,022.8</t>
-  </si>
-  <si>
-    <t>KSBBL</t>
-  </si>
-  <si>
-    <t>62,800,854.8</t>
-  </si>
-  <si>
-    <t>61,635,705.9</t>
-  </si>
-  <si>
-    <t>GBIME</t>
-  </si>
-  <si>
-    <t>55,703,062.0</t>
-  </si>
-  <si>
-    <t>NMB</t>
-  </si>
-  <si>
-    <t>48,045,252.0</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>1,113,815,579.2</t>
-  </si>
-  <si>
-    <t>JBBL</t>
-  </si>
-  <si>
-    <t>440,471,926.0</t>
-  </si>
-  <si>
-    <t>CHDC</t>
-  </si>
-  <si>
-    <t>308,421,471.0</t>
-  </si>
-  <si>
-    <t>CBBL</t>
-  </si>
-  <si>
-    <t>194,213,422.0</t>
-  </si>
-  <si>
-    <t>64,018,589.6</t>
-  </si>
-  <si>
-    <t>201,547,553.8</t>
-  </si>
-  <si>
-    <t>RADHI</t>
-  </si>
-  <si>
-    <t>142,569,142.79</t>
-  </si>
-  <si>
-    <t>MDB</t>
-  </si>
-  <si>
-    <t>112,367,590.0</t>
-  </si>
-  <si>
-    <t>106,643,273.0</t>
-  </si>
-  <si>
-    <t>PRVU</t>
-  </si>
-  <si>
-    <t>77,354,499.0</t>
-  </si>
-  <si>
-    <t>144,298,420.0</t>
-  </si>
-  <si>
-    <t>NGPL</t>
-  </si>
-  <si>
-    <t>128,490,855.0</t>
-  </si>
-  <si>
-    <t>CLI</t>
-  </si>
-  <si>
-    <t>99,824,932.0</t>
-  </si>
-  <si>
-    <t>87,224,590.0</t>
-  </si>
-  <si>
-    <t>PCBL</t>
-  </si>
-  <si>
-    <t>21,881,722.0</t>
-  </si>
-  <si>
-    <t>1,577,192,415.0</t>
-  </si>
-  <si>
-    <t>SGHC</t>
-  </si>
-  <si>
-    <t>485,557,229.6</t>
-  </si>
-  <si>
-    <t>PPCL</t>
-  </si>
-  <si>
-    <t>78,793,640.0</t>
-  </si>
-  <si>
-    <t>HBL</t>
-  </si>
-  <si>
-    <t>19,372,300.0</t>
-  </si>
-  <si>
-    <t>AHPC</t>
-  </si>
-  <si>
-    <t>5,624,640.0</t>
-  </si>
-  <si>
-    <t>NIMB</t>
-  </si>
-  <si>
-    <t>1,376,484,450.0</t>
-  </si>
-  <si>
-    <t>SANIMA</t>
-  </si>
-  <si>
-    <t>104,405,554.0</t>
-  </si>
-  <si>
-    <t>44,347,287.0</t>
-  </si>
-  <si>
-    <t>39,618,000.0</t>
-  </si>
-  <si>
-    <t>HIDCLP</t>
-  </si>
-  <si>
-    <t>17,801,802.2</t>
-  </si>
-  <si>
-    <t>317,728,341.2</t>
-  </si>
-  <si>
-    <t>229,332,919.5</t>
-  </si>
-  <si>
-    <t>100,736,465.6</t>
-  </si>
-  <si>
-    <t>GCIL</t>
-  </si>
-  <si>
-    <t>74,393,109.0</t>
-  </si>
-  <si>
-    <t>MKHC</t>
-  </si>
-  <si>
-    <t>47,010,191.0</t>
-  </si>
-  <si>
-    <t>352,665,135.6</t>
-  </si>
-  <si>
-    <t>LBBL</t>
-  </si>
-  <si>
-    <t>228,670,928.4</t>
-  </si>
-  <si>
-    <t>163,615,144.0</t>
-  </si>
-  <si>
-    <t>SRLI</t>
-  </si>
-  <si>
-    <t>133,638,934.0</t>
-  </si>
-  <si>
-    <t>KBL</t>
-  </si>
-  <si>
-    <t>116,983,145.2</t>
+    <t>211,428,992.5</t>
+  </si>
+  <si>
+    <t>BFC</t>
+  </si>
+  <si>
+    <t>92,617,308.8</t>
+  </si>
+  <si>
+    <t>54,248,771.6</t>
+  </si>
+  <si>
+    <t>58,312,867.3</t>
+  </si>
+  <si>
+    <t>BARUN</t>
+  </si>
+  <si>
+    <t>36,877,794.0</t>
+  </si>
+  <si>
+    <t>ILI</t>
+  </si>
+  <si>
+    <t>12,852,184.3</t>
+  </si>
+  <si>
+    <t>GMFBS</t>
+  </si>
+  <si>
+    <t>12,405,773.0</t>
+  </si>
+  <si>
+    <t>6,918,262.8</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -557,109 +542,109 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>2,195,306,379.69</t>
-  </si>
-  <si>
-    <t>1,520,032,155.1</t>
-  </si>
-  <si>
-    <t>1,514,027,827.5</t>
-  </si>
-  <si>
-    <t>1,391,864,391.9</t>
-  </si>
-  <si>
-    <t>1,132,705,598.09</t>
+    <t>2,654,646,718.8</t>
+  </si>
+  <si>
+    <t>1,798,728,226.1</t>
+  </si>
+  <si>
+    <t>1,571,859,758.4</t>
+  </si>
+  <si>
+    <t>1,071,588,396.8</t>
+  </si>
+  <si>
+    <t>1,050,613,769.8</t>
+  </si>
+  <si>
+    <t>Hydro Power</t>
+  </si>
+  <si>
+    <t>8,487,083,168.3</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>8,318,015,433.65</t>
-  </si>
-  <si>
-    <t>Hydro Power</t>
-  </si>
-  <si>
-    <t>8,164,490,177.9</t>
+    <t>7,350,784,336.95</t>
+  </si>
+  <si>
+    <t>Commercial Banks</t>
+  </si>
+  <si>
+    <t>3,906,230,429.3</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>3,729,786,825.1</t>
+  </si>
+  <si>
+    <t>Investment</t>
+  </si>
+  <si>
+    <t>2,916,989,802.2</t>
   </si>
   <si>
     <t>Microfinance</t>
   </si>
   <si>
-    <t>3,032,329,108.5</t>
+    <t>1,732,977,896.1</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>2,163,032,772.19</t>
-  </si>
-  <si>
-    <t>Commercial Banks</t>
-  </si>
-  <si>
-    <t>2,028,915,116.3</t>
-  </si>
-  <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>1,266,505,022.9</t>
-  </si>
-  <si>
-    <t>Investment</t>
-  </si>
-  <si>
-    <t>1,031,826,154.3</t>
+    <t>821,687,761.5</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>821,313,566.9</t>
+  </si>
+  <si>
+    <t>Hotels And Tourism</t>
+  </si>
+  <si>
+    <t>414,580,747.8</t>
   </si>
   <si>
     <t>Manufacturing And Processing</t>
   </si>
   <si>
-    <t>436,877,908.0</t>
+    <t>286,099,340.0</t>
   </si>
   <si>
     <t>Non Life Insurance</t>
   </si>
   <si>
-    <t>184,770,518.5</t>
-  </si>
-  <si>
-    <t>Hotels And Tourism</t>
-  </si>
-  <si>
-    <t>126,161,561.2</t>
-  </si>
-  <si>
-    <t>Others</t>
-  </si>
-  <si>
-    <t>79,068,829.09</t>
+    <t>274,909,249.2</t>
   </si>
   <si>
     <t>Life Insurance</t>
   </si>
   <si>
-    <t>70,680,936.8</t>
+    <t>202,584,621.1</t>
+  </si>
+  <si>
+    <t>Trading</t>
+  </si>
+  <si>
+    <t>87,650,884.0</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>10,978,424.65</t>
-  </si>
-  <si>
-    <t>Trading</t>
-  </si>
-  <si>
-    <t>10,922,275.0</t>
+    <t>56,329,496.94</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>1,897,325.0</t>
+    <t>4,140,228.5</t>
   </si>
   <si>
     <t>Total</t>
@@ -671,211 +656,211 @@
     <t>100%</t>
   </si>
   <si>
-    <t>220,445,372.5</t>
-  </si>
-  <si>
-    <t>209,668,730.0</t>
-  </si>
-  <si>
-    <t>154,934,403.0</t>
-  </si>
-  <si>
-    <t>86,258,340.5</t>
-  </si>
-  <si>
-    <t>61,528,331.0</t>
-  </si>
-  <si>
-    <t>994,288,406.0</t>
-  </si>
-  <si>
-    <t>502,346,917.5</t>
-  </si>
-  <si>
-    <t>236,693,721.9</t>
-  </si>
-  <si>
-    <t>17,419,423.5</t>
-  </si>
-  <si>
-    <t>14,500,923.3</t>
-  </si>
-  <si>
-    <t>1,416,414,890.8</t>
-  </si>
-  <si>
-    <t>465,202,863.9</t>
-  </si>
-  <si>
-    <t>132,366,986.3</t>
-  </si>
-  <si>
-    <t>56,342,493.6</t>
-  </si>
-  <si>
-    <t>30,706,888.0</t>
-  </si>
-  <si>
-    <t>130,878,034.7</t>
-  </si>
-  <si>
-    <t>70,703,865.9</t>
-  </si>
-  <si>
-    <t>16,503,192.4</t>
-  </si>
-  <si>
-    <t>7,303,304.0</t>
-  </si>
-  <si>
-    <t>5,371,015.0</t>
-  </si>
-  <si>
-    <t>485,890,175.3</t>
-  </si>
-  <si>
-    <t>43,077,023.0</t>
-  </si>
-  <si>
-    <t>21,272,784.0</t>
-  </si>
-  <si>
-    <t>17,111,386.2</t>
-  </si>
-  <si>
-    <t>6,690,492.7</t>
-  </si>
-  <si>
-    <t>391,586,252.6</t>
-  </si>
-  <si>
-    <t>306,594,996.0</t>
-  </si>
-  <si>
-    <t>66,011,033.2</t>
-  </si>
-  <si>
-    <t>54,762,211.0</t>
-  </si>
-  <si>
-    <t>44,221,725.0</t>
-  </si>
-  <si>
-    <t>172,697,509.3</t>
-  </si>
-  <si>
-    <t>149,752,836.8</t>
-  </si>
-  <si>
-    <t>102,323,224.8</t>
-  </si>
-  <si>
-    <t>57,034,394.2</t>
-  </si>
-  <si>
-    <t>43,947,079.7</t>
-  </si>
-  <si>
-    <t>1,168,721,987.59</t>
-  </si>
-  <si>
-    <t>444,509,319.7</t>
-  </si>
-  <si>
-    <t>316,084,161.39</t>
-  </si>
-  <si>
-    <t>244,507,506.2</t>
-  </si>
-  <si>
-    <t>114,325,248.9</t>
-  </si>
-  <si>
-    <t>338,933,104.0</t>
-  </si>
-  <si>
-    <t>236,813,149.0</t>
-  </si>
-  <si>
-    <t>204,279,507.1</t>
-  </si>
-  <si>
-    <t>179,565,220.9</t>
-  </si>
-  <si>
-    <t>108,533,358.8</t>
-  </si>
-  <si>
-    <t>272,822,516.3</t>
-  </si>
-  <si>
-    <t>167,820,874.1</t>
-  </si>
-  <si>
-    <t>87,475,930.0</t>
-  </si>
-  <si>
-    <t>35,012,469.9</t>
-  </si>
-  <si>
-    <t>27,952,356.0</t>
-  </si>
-  <si>
-    <t>1,593,030,490.7</t>
-  </si>
-  <si>
-    <t>584,914,452.9</t>
-  </si>
-  <si>
-    <t>21,012,896.7</t>
-  </si>
-  <si>
-    <t>10,460,246.0</t>
-  </si>
-  <si>
-    <t>3,457,804.4</t>
-  </si>
-  <si>
-    <t>1,426,329,138.3</t>
-  </si>
-  <si>
-    <t>106,473,143.0</t>
-  </si>
-  <si>
-    <t>57,429,801.2</t>
-  </si>
-  <si>
-    <t>2,987,787.3</t>
-  </si>
-  <si>
-    <t>476,842,308.8</t>
-  </si>
-  <si>
-    <t>384,126,626.8</t>
-  </si>
-  <si>
-    <t>112,849,869.0</t>
-  </si>
-  <si>
-    <t>62,215,278.2</t>
-  </si>
-  <si>
-    <t>45,191,860.7</t>
-  </si>
-  <si>
-    <t>598,304,481.9</t>
-  </si>
-  <si>
-    <t>299,628,610.39</t>
-  </si>
-  <si>
-    <t>232,901,174.7</t>
-  </si>
-  <si>
-    <t>170,930,359.6</t>
-  </si>
-  <si>
-    <t>91,256,539.0</t>
+    <t>246,060,479.39</t>
+  </si>
+  <si>
+    <t>157,606,840.19</t>
+  </si>
+  <si>
+    <t>16,983,602.0</t>
+  </si>
+  <si>
+    <t>12,838,156.9</t>
+  </si>
+  <si>
+    <t>8,875,603.8</t>
+  </si>
+  <si>
+    <t>429,788,521.0</t>
+  </si>
+  <si>
+    <t>356,743,453.9</t>
+  </si>
+  <si>
+    <t>280,161,105.89</t>
+  </si>
+  <si>
+    <t>187,321,743.2</t>
+  </si>
+  <si>
+    <t>185,267,841.9</t>
+  </si>
+  <si>
+    <t>729,257,207.7</t>
+  </si>
+  <si>
+    <t>663,080,253.1</t>
+  </si>
+  <si>
+    <t>183,017,055.7</t>
+  </si>
+  <si>
+    <t>75,348,001.0</t>
+  </si>
+  <si>
+    <t>38,925,108.5</t>
+  </si>
+  <si>
+    <t>1,322,053,126.3</t>
+  </si>
+  <si>
+    <t>658,009,132.79</t>
+  </si>
+  <si>
+    <t>133,471,972.7</t>
+  </si>
+  <si>
+    <t>88,399,744.3</t>
+  </si>
+  <si>
+    <t>52,884,998.9</t>
+  </si>
+  <si>
+    <t>757,303,590.0</t>
+  </si>
+  <si>
+    <t>493,056,129.3</t>
+  </si>
+  <si>
+    <t>250,958,178.4</t>
+  </si>
+  <si>
+    <t>52,553,050.4</t>
+  </si>
+  <si>
+    <t>41,402,318.9</t>
+  </si>
+  <si>
+    <t>231,303,842.0</t>
+  </si>
+  <si>
+    <t>203,959,659.2</t>
+  </si>
+  <si>
+    <t>121,527,294.1</t>
+  </si>
+  <si>
+    <t>45,349,867.3</t>
+  </si>
+  <si>
+    <t>911,575,883.3</t>
+  </si>
+  <si>
+    <t>163,755,151.5</t>
+  </si>
+  <si>
+    <t>159,011,224.9</t>
+  </si>
+  <si>
+    <t>112,662,100.3</t>
+  </si>
+  <si>
+    <t>89,541,506.3</t>
+  </si>
+  <si>
+    <t>2,607,448,019.1</t>
+  </si>
+  <si>
+    <t>946,138,009.9</t>
+  </si>
+  <si>
+    <t>168,915,881.4</t>
+  </si>
+  <si>
+    <t>93,606,377.8</t>
+  </si>
+  <si>
+    <t>37,499,343.9</t>
+  </si>
+  <si>
+    <t>881,093,002.8</t>
+  </si>
+  <si>
+    <t>648,549,710.9</t>
+  </si>
+  <si>
+    <t>155,662,562.6</t>
+  </si>
+  <si>
+    <t>131,595,981.4</t>
+  </si>
+  <si>
+    <t>126,902,285.7</t>
+  </si>
+  <si>
+    <t>821,941,954.5</t>
+  </si>
+  <si>
+    <t>240,658,748.4</t>
+  </si>
+  <si>
+    <t>139,427,473.19</t>
+  </si>
+  <si>
+    <t>47,104,169.5</t>
+  </si>
+  <si>
+    <t>41,461,387.7</t>
+  </si>
+  <si>
+    <t>634,407,741.79</t>
+  </si>
+  <si>
+    <t>58,389,448.7</t>
+  </si>
+  <si>
+    <t>14,178,634.9</t>
+  </si>
+  <si>
+    <t>10,737,188.1</t>
+  </si>
+  <si>
+    <t>8,732,787.0</t>
+  </si>
+  <si>
+    <t>410,545,443.4</t>
+  </si>
+  <si>
+    <t>300,811,255.8</t>
+  </si>
+  <si>
+    <t>259,699,905.8</t>
+  </si>
+  <si>
+    <t>80,621,613.7</t>
+  </si>
+  <si>
+    <t>25,794,191.4</t>
+  </si>
+  <si>
+    <t>575,999,139.4</t>
+  </si>
+  <si>
+    <t>373,353,736.8</t>
+  </si>
+  <si>
+    <t>363,922,721.2</t>
+  </si>
+  <si>
+    <t>66,013,471.4</t>
+  </si>
+  <si>
+    <t>46,814,974.2</t>
+  </si>
+  <si>
+    <t>122,388,984.1</t>
+  </si>
+  <si>
+    <t>73,323,098.09</t>
+  </si>
+  <si>
+    <t>63,975,949.0</t>
+  </si>
+  <si>
+    <t>31,613,981.1</t>
+  </si>
+  <si>
+    <t>28,850,192.9</t>
   </si>
 </sst>
 </file>
@@ -1684,7 +1669,7 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.06720960802695257</v>
+        <v>0.03890029705462798</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>64</v>
@@ -1693,52 +1678,52 @@
         <v>65</v>
       </c>
       <c r="G9" s="12">
-        <v>0.274244444882751</v>
+        <v>0.1107769764621098</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="I9" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="14">
+        <v>0.1615733575444689</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="M9" s="16">
+        <v>0.3060004700034574</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="O9" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="P9" s="18">
+        <v>0.2185921019344255</v>
+      </c>
+      <c r="Q9" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="R9" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="S9" s="16">
+        <v>0.1039534862585125</v>
+      </c>
+      <c r="T9" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="J9" s="14">
-        <v>0.3562440659149559</v>
-      </c>
-      <c r="K9" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="L9" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="M9" s="16">
-        <v>0.04742526023898697</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="O9" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="P9" s="18">
-        <v>0.1181710364064338</v>
-      </c>
-      <c r="Q9" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="R9" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="S9" s="16">
-        <v>0.1283619392289392</v>
-      </c>
-      <c r="T9" s="17" t="s">
-        <v>102</v>
-      </c>
       <c r="U9" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V9" s="18">
-        <v>0.06638558554902807</v>
+        <v>0.3366536978619668</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1750,7 +1735,7 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.06582745730588896</v>
+        <v>0.01751327874540419</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>66</v>
@@ -1759,52 +1744,52 @@
         <v>67</v>
       </c>
       <c r="G10" s="12">
-        <v>0.06327823972903943</v>
+        <v>0.0597574709207694</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="J10" s="14">
-        <v>0.07182771782211887</v>
+        <v>0.1136019451731994</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="M10" s="16">
-        <v>0.02308433743552894</v>
+        <v>0.2080101617313312</v>
       </c>
       <c r="N10" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="O10" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="O10" s="17" t="s">
-        <v>95</v>
-      </c>
       <c r="P10" s="18">
-        <v>0.09510715292737651</v>
+        <v>0.06503162447232783</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="S10" s="16">
-        <v>0.1116974075233301</v>
+        <v>0.08859949945768854</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="V10" s="18">
-        <v>0.03188191725654817</v>
+        <v>0.07660971078815185</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1816,61 +1801,61 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.01780725433567625</v>
+        <v>0.01058270247258452</v>
       </c>
       <c r="E11" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>69</v>
-      </c>
       <c r="G11" s="12">
-        <v>0.0507203573626088</v>
+        <v>0.03708730077242518</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J11" s="14">
-        <v>0.0637539380930178</v>
+        <v>0.05971007301542552</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M11" s="16">
-        <v>0.006434653727757542</v>
+        <v>0.1296380891993505</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="P11" s="18">
-        <v>0.01160820464731979</v>
+        <v>0.05007745226813889</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="S11" s="16">
-        <v>0.03319093247807719</v>
+        <v>0.0340708124314751</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="V11" s="18">
-        <v>0.0312904096896582</v>
+        <v>0.06497282777105992</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1882,61 +1867,61 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.01160198656814849</v>
+        <v>0.004454069591010354</v>
       </c>
       <c r="E12" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>71</v>
-      </c>
       <c r="G12" s="12">
-        <v>0.03878272017151684</v>
+        <v>0.03487074708961372</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J12" s="14">
-        <v>0.04075747012754301</v>
+        <v>0.04760463500570174</v>
       </c>
       <c r="K12" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="L12" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="L12" s="15" t="s">
-        <v>89</v>
-      </c>
       <c r="M12" s="16">
-        <v>0.002931755070813126</v>
+        <v>0.0225909097450869</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="P12" s="18">
-        <v>0.007275893029336976</v>
+        <v>0.04532288687972438</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="S12" s="16">
-        <v>0.02498753211899808</v>
+        <v>0.02332365399855716</v>
       </c>
       <c r="T12" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="U12" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="U12" s="17" t="s">
-        <v>115</v>
-      </c>
       <c r="V12" s="18">
-        <v>0.02827860256482325</v>
+        <v>0.04540612734511738</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1948,61 +1933,61 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.01066560942354198</v>
+        <v>0.003352464480199103</v>
       </c>
       <c r="E13" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>73</v>
-      </c>
       <c r="G13" s="12">
-        <v>0.03708327829852624</v>
+        <v>0.02897877734053086</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J13" s="14">
-        <v>0.03328262593507585</v>
+        <v>0.02187141622558036</v>
       </c>
       <c r="K13" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="L13" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="L13" s="15" t="s">
-        <v>91</v>
-      </c>
       <c r="M13" s="16">
-        <v>0.002530553155249073</v>
+        <v>0.01511903837315097</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="P13" s="18">
-        <v>0.006599110918149557</v>
+        <v>0.0391151540386909</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="S13" s="16">
-        <v>0.02073466893326937</v>
+        <v>0.01111262884483541</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>116</v>
+        <v>54</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="V13" s="18">
-        <v>0.0243909856595456</v>
+        <v>0.04056144255609538</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -2013,7 +1998,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -2022,7 +2007,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -2031,7 +2016,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -2040,7 +2025,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2049,7 +2034,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2058,7 +2043,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2067,7 +2052,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2076,566 +2061,566 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C16" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D16" s="10">
+        <v>0.5811549393460262</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="G16" s="12">
+        <v>0.1667892751606596</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="J16" s="14">
+        <v>0.1910520579400396</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="M16" s="16">
+        <v>0.150862535606682</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="O16" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="P16" s="18">
+        <v>0.06569828405357005</v>
+      </c>
+      <c r="Q16" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="R16" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="S16" s="16">
+        <v>0.2279265410693836</v>
+      </c>
+      <c r="T16" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="D16" s="10">
-        <v>0.3499412224614967</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="G16" s="12">
-        <v>0.06971745129230797</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="J16" s="14">
-        <v>0.05168241396911392</v>
-      </c>
-      <c r="K16" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="L16" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="M16" s="16">
-        <v>0.6393282904008641</v>
-      </c>
-      <c r="N16" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="O16" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="P16" s="18">
-        <v>0.6171406960455069</v>
-      </c>
-      <c r="Q16" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="R16" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="S16" s="16">
-        <v>0.157491002837348</v>
-      </c>
-      <c r="T16" s="17" t="s">
-        <v>76</v>
-      </c>
       <c r="U16" s="17" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="V16" s="18">
-        <v>0.1790364272632247</v>
+        <v>0.03032014774940489</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D17" s="10">
-        <v>0.138388515228994</v>
+        <v>0.2107356044719484</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G17" s="12">
-        <v>0.0493161890657742</v>
+        <v>0.1260484898474794</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="J17" s="14">
-        <v>0.04602072260635557</v>
+        <v>0.06180230910147887</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="M17" s="16">
-        <v>0.1968247314275525</v>
+        <v>0.01898650620052333</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="P17" s="18">
-        <v>0.04680976691496716</v>
+        <v>0.06459966025915749</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="S17" s="16">
-        <v>0.1136753219409431</v>
+        <v>0.1666578231455578</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="V17" s="18">
-        <v>0.1160886685610345</v>
+        <v>0.01917484449872211</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D18" s="10">
-        <v>0.09690058983789177</v>
+        <v>0.03533326874423899</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G18" s="12">
-        <v>0.03886914941390388</v>
+        <v>0.03357434915332656</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="J18" s="14">
-        <v>0.03575363791275502</v>
+        <v>0.0242007162405876</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="M18" s="16">
-        <v>0.0319396686647527</v>
+        <v>0.01638514369202454</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="P18" s="18">
-        <v>0.01988290936879807</v>
+        <v>0.04324948062337386</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="S18" s="16">
-        <v>0.04993286695708219</v>
+        <v>0.0953651471805782</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>102</v>
+        <v>165</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="V18" s="18">
-        <v>0.08306199811353862</v>
+        <v>0.006682575303214115</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D19" s="10">
-        <v>0.06101843391517767</v>
+        <v>0.007168860493121855</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G19" s="12">
-        <v>0.03688904703059612</v>
+        <v>0.03010964675073163</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>56</v>
+        <v>135</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="J19" s="14">
-        <v>0.03124065647195745</v>
+        <v>0.01441258139059072</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="M19" s="16">
-        <v>0.007852725718397941</v>
+        <v>0.01079489099572445</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="P19" s="18">
-        <v>0.01776255452499365</v>
+        <v>0.03606112643740466</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="S19" s="16">
-        <v>0.03687504015646856</v>
+        <v>0.04177508098933528</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="V19" s="18">
-        <v>0.06784406756261702</v>
+        <v>0.006450460896913879</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="10">
+        <v>0.005256500368872186</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="G20" s="12">
+        <v>0.02084290053275661</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="J20" s="14">
+        <v>0.01239157215626106</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="M20" s="16">
+        <v>0.00365114409329114</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="O20" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="P20" s="18">
+        <v>0.01666465276732626</v>
+      </c>
+      <c r="Q20" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="R20" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="S20" s="16">
+        <v>0.02446893411744168</v>
+      </c>
+      <c r="T20" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="D20" s="10">
-        <v>0.02011351243710891</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="G20" s="12">
-        <v>0.0267577473136932</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="J20" s="14">
-        <v>0.007837232138515912</v>
-      </c>
-      <c r="K20" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="L20" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="M20" s="16">
-        <v>0.002279995415347161</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="O20" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="P20" s="18">
-        <v>0.007981359034293803</v>
-      </c>
-      <c r="Q20" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="R20" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="S20" s="16">
-        <v>0.02330192546312666</v>
-      </c>
-      <c r="T20" s="17" t="s">
-        <v>173</v>
-      </c>
       <c r="U20" s="17" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="V20" s="18">
-        <v>0.05938847436957434</v>
+        <v>0.003597194924167476</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>152</v>
+        <v>113</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D31" s="22">
-        <v>0.2776510872721578</v>
+        <v>0.2832944815075559</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D32" s="22">
-        <v>0.2725264930077277</v>
+        <v>0.2453654095423734</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D33" s="22">
-        <v>0.1012175897794161</v>
+        <v>0.1303879674763739</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D34" s="22">
-        <v>0.07220092410228988</v>
+        <v>0.1244983704998928</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D35" s="22">
-        <v>0.06772414556297815</v>
+        <v>0.09736762291474067</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D36" s="22">
-        <v>0.0422752878314304</v>
+        <v>0.05784591299557662</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D37" s="22">
-        <v>0.03444182760929689</v>
+        <v>0.02742751587785766</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D38" s="22">
-        <v>0.01458276041069554</v>
+        <v>0.02741502545410573</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D39" s="22">
-        <v>0.0061675451033461</v>
+        <v>0.01383849264370308</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D40" s="22">
-        <v>0.004211208180430361</v>
+        <v>0.00954984917405831</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D41" s="22">
-        <v>0.002639276945813271</v>
+        <v>0.009176329684694869</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D42" s="22">
-        <v>0.002359293404595577</v>
+        <v>0.006762170707869339</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D43" s="22">
-        <v>0.0003664541818805451</v>
+        <v>0.002925741534995785</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D44" s="22">
-        <v>0.0003645799353734536</v>
+        <v>0.001880249705670692</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D45" s="22">
-        <v>6.33317349986553E-05</v>
+        <v>0.000138198703013917</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -3014,331 +2999,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="C9" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="D9" s="10">
+        <v>0.05586295158753527</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="F9" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="D9" s="10">
-        <v>0.06926005038826809</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="F9" s="11" t="s">
+      <c r="G9" s="12">
+        <v>0.1111341168554788</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="I9" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="G9" s="12">
-        <v>0.3439349781669815</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="I9" s="13" t="s">
+      <c r="J9" s="14">
+        <v>0.2304029891453169</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="L9" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="J9" s="14">
-        <v>0.5073079853427562</v>
-      </c>
-      <c r="K9" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="L9" s="15" t="s">
+      <c r="M9" s="16">
+        <v>0.4364902525995035</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="O9" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="M9" s="16">
-        <v>0.05305251875420411</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="O9" s="17" t="s">
+      <c r="P9" s="18">
+        <v>0.2654050307793339</v>
+      </c>
+      <c r="Q9" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="R9" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="P9" s="18">
-        <v>0.2178467043244225</v>
-      </c>
-      <c r="Q9" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="R9" s="15" t="s">
-        <v>243</v>
-      </c>
       <c r="S9" s="16">
-        <v>0.1941007572266679</v>
+        <v>0.104329707458466</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="V9" s="18">
-        <v>0.08767281463682493</v>
+        <v>0.473979702014246</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="C10" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0.03578137905536816</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="D10" s="10">
-        <v>0.06587421926783325</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="F10" s="11" t="s">
+      <c r="G10" s="12">
+        <v>0.09224622519210954</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="I10" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="G10" s="12">
-        <v>0.1737671635915796</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="I10" s="13" t="s">
+      <c r="J10" s="14">
+        <v>0.2094949089900826</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="L10" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="J10" s="14">
-        <v>0.1666186434452793</v>
-      </c>
-      <c r="K10" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="L10" s="15" t="s">
+      <c r="M10" s="16">
+        <v>0.2172488887738371</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="O10" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="M10" s="16">
-        <v>0.02866041028391514</v>
-      </c>
-      <c r="N10" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="O10" s="17" t="s">
+      <c r="P10" s="18">
+        <v>0.1727967210254553</v>
+      </c>
+      <c r="Q10" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="R10" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="P10" s="18">
-        <v>0.0193133921402369</v>
-      </c>
-      <c r="Q10" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="R10" s="15" t="s">
-        <v>244</v>
-      </c>
       <c r="S10" s="16">
-        <v>0.1519724466586323</v>
+        <v>0.0919961008588194</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="V10" s="18">
-        <v>0.07602456315277673</v>
+        <v>0.08514553679314929</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C11" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D11" s="10">
+        <v>0.003855776184056184</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="D11" s="10">
-        <v>0.04867765849181631</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="F11" s="11" t="s">
+      <c r="G11" s="12">
+        <v>0.07244366836277313</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="I11" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="G11" s="12">
-        <v>0.08187488618260937</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="I11" s="13" t="s">
+      <c r="J11" s="14">
+        <v>0.05782277672763405</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="L11" s="15" t="s">
         <v>230</v>
       </c>
-      <c r="J11" s="14">
-        <v>0.04740901100511447</v>
-      </c>
-      <c r="K11" s="15" t="s">
-        <v>189</v>
-      </c>
-      <c r="L11" s="15" t="s">
+      <c r="M11" s="16">
+        <v>0.04406722689112032</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="O11" s="17" t="s">
         <v>235</v>
       </c>
-      <c r="M11" s="16">
-        <v>0.006689708676571674</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="O11" s="17" t="s">
+      <c r="P11" s="18">
+        <v>0.08795094060306459</v>
+      </c>
+      <c r="Q11" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="R11" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="P11" s="18">
-        <v>0.009537558324458895</v>
-      </c>
-      <c r="Q11" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="R11" s="15" t="s">
-        <v>245</v>
-      </c>
       <c r="S11" s="16">
-        <v>0.03272022816011062</v>
+        <v>0.05481494354802789</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="V11" s="18">
-        <v>0.05194611756298542</v>
+        <v>0.08267890186188548</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C12" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="D12" s="10">
+        <v>0.00291463846257093</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="D12" s="10">
-        <v>0.02710085016385811</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="F12" s="11" t="s">
+      <c r="G12" s="12">
+        <v>0.0484373953262488</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="I12" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="G12" s="12">
-        <v>0.006025564619883443</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="I12" s="13" t="s">
+      <c r="J12" s="14">
+        <v>0.02380559900295974</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="L12" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="J12" s="14">
-        <v>0.02017981955926719</v>
-      </c>
-      <c r="K12" s="15" t="s">
-        <v>207</v>
-      </c>
-      <c r="L12" s="15" t="s">
+      <c r="M12" s="16">
+        <v>0.02918613930986816</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="O12" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="M12" s="16">
-        <v>0.002960456071301733</v>
-      </c>
-      <c r="N12" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="O12" s="17" t="s">
-        <v>241</v>
-      </c>
       <c r="P12" s="18">
-        <v>0.007671814083894287</v>
+        <v>0.01841777081627183</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>246</v>
+        <v>103</v>
       </c>
       <c r="S12" s="16">
-        <v>0.02714443255331625</v>
+        <v>0.0340708124314751</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="V12" s="18">
-        <v>0.02895447589770308</v>
+        <v>0.05857937853202209</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C13" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="D13" s="10">
+        <v>0.002015022593626403</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="D13" s="10">
-        <v>0.01933111707920309</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>193</v>
-      </c>
-      <c r="F13" s="11" t="s">
+      <c r="G13" s="12">
+        <v>0.04790630039017948</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="I13" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="G13" s="12">
-        <v>0.005016024232496756</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="I13" s="13" t="s">
+      <c r="J13" s="14">
+        <v>0.01229807707967859</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="L13" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="J13" s="14">
-        <v>0.01099808367492324</v>
-      </c>
-      <c r="K13" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="L13" s="15" t="s">
+      <c r="M13" s="16">
+        <v>0.01746055893622788</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="O13" s="17" t="s">
         <v>237</v>
       </c>
-      <c r="M13" s="16">
-        <v>0.002177186375618854</v>
-      </c>
-      <c r="N13" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="O13" s="17" t="s">
-        <v>242</v>
-      </c>
       <c r="P13" s="18">
-        <v>0.002999652718027714</v>
+        <v>0.01450987934969422</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="S13" s="16">
-        <v>0.02191974373813722</v>
+        <v>0.02045507911921867</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="V13" s="18">
-        <v>0.02231047910294252</v>
+        <v>0.04655767802932697</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3349,7 +3334,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3358,7 +3343,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3367,7 +3352,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3376,7 +3361,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3385,7 +3370,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3394,7 +3379,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3403,7 +3388,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3412,331 +3397,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D16" s="10">
-        <v>0.3671918481802235</v>
+        <v>0.5919672383520441</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="G16" s="12">
-        <v>0.1172405803194162</v>
+        <v>0.2278318008724106</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="J16" s="14">
-        <v>0.09771504239278525</v>
+        <v>0.2596859944902318</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="M16" s="16">
-        <v>0.6457483883953884</v>
+        <v>0.209456632234101</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="P16" s="18">
-        <v>0.6394883408965863</v>
+        <v>0.1438799808698811</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="R16" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="S16" s="16">
+        <v>0.2598046845669351</v>
+      </c>
+      <c r="T16" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="U16" s="17" t="s">
         <v>277</v>
       </c>
-      <c r="S16" s="16">
-        <v>0.2363603231759434</v>
-      </c>
-      <c r="T16" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="U16" s="17" t="s">
-        <v>282</v>
-      </c>
       <c r="V16" s="18">
-        <v>0.3037394004732196</v>
+        <v>0.06363693388151342</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="D17" s="10">
-        <v>0.1396569931649473</v>
+        <v>0.2148011008149351</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="G17" s="12">
-        <v>0.08191619729192451</v>
+        <v>0.1677010804989544</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="J17" s="14">
-        <v>0.06010729630923712</v>
+        <v>0.07603420906899148</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="M17" s="16">
-        <v>0.2371000225760747</v>
+        <v>0.01927791304691139</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="P17" s="18">
-        <v>0.04773676126974976</v>
+        <v>0.1054224774035062</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="R17" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="S17" s="16">
+        <v>0.1684013797698575</v>
+      </c>
+      <c r="T17" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="U17" s="17" t="s">
         <v>278</v>
       </c>
-      <c r="S17" s="16">
-        <v>0.190403183558558</v>
-      </c>
-      <c r="T17" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="U17" s="17" t="s">
-        <v>283</v>
-      </c>
       <c r="V17" s="18">
-        <v>0.152111537253587</v>
+        <v>0.03812481311197861</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="D18" s="10">
-        <v>0.09930807209617186</v>
+        <v>0.03834886336897079</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="G18" s="12">
-        <v>0.07066246311475168</v>
+        <v>0.04025100852335625</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="J18" s="14">
-        <v>0.03133067726308598</v>
+        <v>0.04405099634952646</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="M18" s="16">
-        <v>0.008517755472201505</v>
+        <v>0.00468123088694453</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="P18" s="18">
-        <v>0.02574839656657443</v>
+        <v>0.09101457117381304</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="R18" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="S18" s="16">
+        <v>0.1641475157178102</v>
+      </c>
+      <c r="T18" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="U18" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="S18" s="16">
-        <v>0.05593721659121971</v>
-      </c>
-      <c r="T18" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="U18" s="17" t="s">
-        <v>284</v>
-      </c>
       <c r="V18" s="18">
-        <v>0.1182362247199582</v>
+        <v>0.03326470324480841</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="D19" s="10">
-        <v>0.07681994866878765</v>
+        <v>0.02125139544585451</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="G19" s="12">
-        <v>0.06211352758124257</v>
+        <v>0.03402790549312742</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="J19" s="14">
-        <v>0.01254018556442226</v>
+        <v>0.01488218606468998</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="M19" s="16">
-        <v>0.004240149222599753</v>
+        <v>0.003544999707457962</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>156</v>
+        <v>270</v>
       </c>
       <c r="P19" s="18">
-        <v>0.01988290936879807</v>
+        <v>0.02825469487808459</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="R19" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="S19" s="16">
+        <v>0.0297754075329186</v>
+      </c>
+      <c r="T19" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="U19" s="17" t="s">
         <v>280</v>
       </c>
-      <c r="S19" s="16">
-        <v>0.03083875526657802</v>
-      </c>
-      <c r="T19" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="U19" s="17" t="s">
-        <v>285</v>
-      </c>
       <c r="V19" s="18">
-        <v>0.08677569117099379</v>
+        <v>0.01643789136568309</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="D20" s="10">
-        <v>0.03591897806548555</v>
+        <v>0.008513451806475007</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="G20" s="12">
-        <v>0.03754284789404169</v>
+        <v>0.03281421619962519</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="J20" s="14">
-        <v>0.01001151110458483</v>
+        <v>0.01309939423200421</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="M20" s="16">
-        <v>0.001401650270802618</v>
+        <v>0.002883224832420761</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="O20" s="17" t="s">
+        <v>271</v>
+      </c>
+      <c r="P20" s="18">
+        <v>0.009039846440507471</v>
+      </c>
+      <c r="Q20" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="R20" s="15" t="s">
         <v>276</v>
       </c>
-      <c r="P20" s="18">
-        <v>0.001339561179901397</v>
-      </c>
-      <c r="Q20" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="R20" s="15" t="s">
+      <c r="S20" s="16">
+        <v>0.02111591628020444</v>
+      </c>
+      <c r="T20" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="U20" s="17" t="s">
         <v>281</v>
       </c>
-      <c r="S20" s="16">
-        <v>0.02240061882691357</v>
-      </c>
-      <c r="T20" s="17" t="s">
-        <v>201</v>
-      </c>
-      <c r="U20" s="17" t="s">
-        <v>286</v>
-      </c>
       <c r="V20" s="18">
-        <v>0.04632792714020448</v>
+        <v>0.0150008420410298</v>
       </c>
     </row>
   </sheetData>
